--- a/PRODUKSI/REPORT/LF_Ball_Mill_Metallurgical_Report.xlsx
+++ b/PRODUKSI/REPORT/LF_Ball_Mill_Metallurgical_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamxi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4B1B67-D073-4DC2-8F84-577549D9187F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C2D6AE-724D-46C9-BF2C-285A81FAAB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="57">
   <si>
     <t>Periode</t>
   </si>
@@ -221,13 +221,23 @@
   <si>
     <t xml:space="preserve">Leach Feed BALL MILL </t>
   </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -289,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -297,14 +307,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -322,6 +326,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -973,6 +985,7 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -986,6 +999,24 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Au (g/t)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -993,6 +1024,7 @@
         <c:crossAx val="48650112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="0.4"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1006,7 +1038,7 @@
   <c:spPr>
     <a:ln w="9525">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1653,6 +1685,8 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="5"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1666,6 +1700,29 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Ag</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-ID" baseline="0"/>
+                  <a:t> (g/t)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-ID"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1673,6 +1730,7 @@
         <c:crossAx val="48650112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="0.5"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1686,7 +1744,7 @@
   <c:spPr>
     <a:ln w="9525">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2333,6 +2391,7 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="30"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2366,7 +2425,7 @@
   <c:spPr>
     <a:ln w="9525">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -2821,16 +2880,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>317948</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114963</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>239423</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>20551</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2858,15 +2917,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>502223</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>87005</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>53623</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>129488</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2893,16 +2952,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>323627</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>169449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>259048</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>67251</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3238,7 +3297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M17"/>
+  <dimension ref="B2:W21"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -3356,10 +3415,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:23">
       <c r="B17" t="s">
         <v>14</v>
       </c>
+    </row>
+    <row r="21" spans="2:23">
+      <c r="W21" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4551,7 +4613,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -4562,29 +4624,29 @@
     <col min="8" max="8" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="15" customFormat="1" ht="27" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" s="13" customFormat="1" ht="27" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4592,25 +4654,25 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="14">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>46265</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>1.0229999999999999</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>0.31</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>6.1559999999999997</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4618,23 +4680,23 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>46265</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>0.94899999999999995</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>0.51300000000000001</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>5.9560000000000004</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4642,23 +4704,23 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>46265</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>0.92900000000000005</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>0.40699999999999997</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>6.2169999999999996</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4666,23 +4728,23 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>46265</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>0.64100000000000001</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>0.55700000000000005</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>7.72</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4690,23 +4752,23 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>46265</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>0.63700000000000001</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>0.502</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>7.51</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4714,23 +4776,23 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>46265</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>0.54900000000000004</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>0.52600000000000002</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>7.64</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4738,23 +4800,23 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>46266</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>0.64600000000000002</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>0.68100000000000005</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>7.62</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4762,23 +4824,23 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>46266</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>0.64500000000000002</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>0.68700000000000006</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>7.55</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4786,23 +4848,23 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>46266</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0.65</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>0.65500000000000003</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>7.43</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4810,23 +4872,23 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>46266</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>0.64100000000000001</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>0.55700000000000005</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>7.72</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4834,23 +4896,23 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>46266</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>0.63700000000000001</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>0.502</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>7.51</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4858,23 +4920,23 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>46266</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>0.54900000000000004</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>0.52600000000000002</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>7.64</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4882,25 +4944,25 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="15">
         <v>2</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="8">
         <v>46267</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <v>0.66</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="7">
         <v>0.32</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <v>9.6300000000000008</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4908,23 +4970,23 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="8">
         <v>46267</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>0.82399999999999995</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="7">
         <v>0.67</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="7">
         <v>9.7899999999999991</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4932,23 +4994,23 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>46267</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="7">
         <v>0.75</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="7">
         <v>0.78</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="7">
         <v>10.1</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4956,23 +5018,23 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="8">
         <v>46267</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="7">
         <v>0.63200000000000001</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="7">
         <v>1.103</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="7">
         <v>9.26</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4980,23 +5042,23 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>46267</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="7">
         <v>0.63100000000000001</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="7">
         <v>1.008</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="7">
         <v>9.24</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5004,23 +5066,23 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="8">
         <v>46267</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="7">
         <v>0.67500000000000004</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="7">
         <v>1.089</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="7">
         <v>9.27</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5028,23 +5090,23 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="8">
         <v>46268</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="7">
         <v>0.66800000000000004</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="7">
         <v>0.61</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="7">
         <v>8.17</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5052,23 +5114,23 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="15"/>
+      <c r="C21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>46268</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="7">
         <v>0.59399999999999997</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="7">
         <v>0.71</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="7">
         <v>7.54</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5076,23 +5138,23 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="8">
         <v>46268</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="7">
         <v>0.72199999999999998</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="7">
         <v>0.85</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="7">
         <v>8.4600000000000009</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5100,25 +5162,25 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="14">
         <v>3</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>46270</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>1.0980000000000001</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
         <v>0.82</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>8.17</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5126,23 +5188,23 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="6" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>46270</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="5">
         <v>1.0880000000000001</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>0.75</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>8.1</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5150,23 +5212,23 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>46270</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="5">
         <v>1.075</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="5">
         <v>0.75</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>8.08</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5174,23 +5236,23 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="14"/>
+      <c r="C26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>46271</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="5">
         <v>0.92</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>9.66</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5198,23 +5260,23 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6" t="s">
+      <c r="B27" s="14"/>
+      <c r="C27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>46271</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>0.86</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>0.54</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>9.56</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5222,23 +5284,23 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="6" t="s">
+      <c r="B28" s="14"/>
+      <c r="C28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>46271</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="5">
         <v>0.92700000000000005</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="5">
         <v>0.6</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>9.74</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5246,23 +5308,23 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="14"/>
+      <c r="C29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>46271</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>0.78800000000000003</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>0.62</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>9.4600000000000009</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5270,23 +5332,23 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="6" t="s">
+      <c r="B30" s="14"/>
+      <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>46271</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="5">
         <v>0.74199999999999999</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="5">
         <v>0.6</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>9.43</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5294,23 +5356,23 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6" t="s">
+      <c r="B31" s="14"/>
+      <c r="C31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>46271</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>0.91300000000000003</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="5">
         <v>0.68</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>9.42</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5318,23 +5380,23 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="6" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>46272</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="5">
         <v>0.91100000000000003</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="5">
         <v>0.95</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>9.3800000000000008</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5342,23 +5404,23 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6" t="s">
+      <c r="B33" s="14"/>
+      <c r="C33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="6">
         <v>46272</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>0.95199999999999996</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="5">
         <v>0.98</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>9.4</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5366,23 +5428,23 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="6" t="s">
+      <c r="B34" s="14"/>
+      <c r="C34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>46272</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="5">
         <v>0.873</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="5">
         <v>0.93</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>9.41</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5390,25 +5452,25 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="15">
         <v>4</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="8">
         <v>46272</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="7">
         <v>0.53100000000000003</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="7">
         <v>1.07</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="7">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5416,23 +5478,23 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="15"/>
+      <c r="C36" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="8">
         <v>46272</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="7">
         <v>0.501</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="7">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="7">
         <v>8.99</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5440,23 +5502,23 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="9" t="s">
+      <c r="B37" s="15"/>
+      <c r="C37" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="8">
         <v>46272</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="7">
         <v>0.55900000000000005</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="7">
         <v>1.02</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="7">
         <v>8.92</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5464,23 +5526,23 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="8">
         <v>46273</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="7">
         <v>0.66400000000000003</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="7">
         <v>0.98</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="7">
         <v>9.0500000000000007</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5488,23 +5550,23 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9" t="s">
+      <c r="B39" s="15"/>
+      <c r="C39" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="8">
         <v>46273</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="7">
         <v>0.64500000000000002</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="7">
         <v>0.94</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="7">
         <v>9.0299999999999994</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5512,23 +5574,23 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9" t="s">
+      <c r="B40" s="15"/>
+      <c r="C40" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="8">
         <v>46273</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="7">
         <v>0.63100000000000001</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="7">
         <v>0.97</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="7">
         <v>9.23</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5536,23 +5598,23 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9" t="s">
+      <c r="B41" s="15"/>
+      <c r="C41" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="8">
         <v>46273</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="7">
         <v>0.61</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="7">
         <v>1.01</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="7">
         <v>7.79</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5560,23 +5622,23 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="9" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="8">
         <v>46273</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="7">
         <v>0.63300000000000001</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="7">
         <v>1.05</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="7">
         <v>7.71</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5584,23 +5646,23 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="9" t="s">
+      <c r="B43" s="15"/>
+      <c r="C43" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="8">
         <v>46273</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="7">
         <v>0.66200000000000003</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="7">
         <v>1.04</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="7">
         <v>7.93</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5608,23 +5670,23 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="9" t="s">
+      <c r="B44" s="15"/>
+      <c r="C44" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="8">
         <v>46274</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="7">
         <v>0.59599999999999997</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="7">
         <v>0.64</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="7">
         <v>7.27</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5632,23 +5694,23 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9" t="s">
+      <c r="B45" s="15"/>
+      <c r="C45" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="8">
         <v>46274</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="7">
         <v>0.59399999999999997</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="7">
         <v>0.68</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="7">
         <v>7.24</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5656,23 +5718,23 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="9" t="s">
+      <c r="B46" s="15"/>
+      <c r="C46" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="8">
         <v>46274</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="7">
         <v>0.58699999999999997</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="7">
         <v>0.68</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="7">
         <v>7.21</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5680,17 +5742,17 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="9" t="s">
+      <c r="B47" s="15"/>
+      <c r="C47" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="8">
         <v>46274</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="12" t="s">
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5698,17 +5760,17 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="9" t="s">
+      <c r="B48" s="15"/>
+      <c r="C48" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="8">
         <v>46274</v>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="12" t="s">
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5716,17 +5778,17 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="9" t="s">
+      <c r="B49" s="15"/>
+      <c r="C49" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="8">
         <v>46274</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="12" t="s">
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5734,25 +5796,25 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="14">
         <v>5</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="6">
         <v>46275</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="5">
         <v>0.79600000000000004</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="5">
         <v>0.64</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <v>9.08</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5760,23 +5822,23 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="6">
         <v>46275</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51" s="5">
         <v>0.82599999999999996</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="5">
         <v>0.72</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>8.82</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5784,23 +5846,23 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="6" t="s">
+      <c r="B52" s="14"/>
+      <c r="C52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="6">
         <v>46275</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="5">
         <v>0.73</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="5">
         <v>0.63</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <v>8.57</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5808,23 +5870,23 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="14"/>
+      <c r="C53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="6">
         <v>46275</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="5">
         <v>0.49299999999999999</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="5">
         <v>0.45</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <v>9.11</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5832,23 +5894,23 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="6" t="s">
+      <c r="B54" s="14"/>
+      <c r="C54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="6">
         <v>46275</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="5">
         <v>0.497</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="5">
         <v>0.52</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <v>9.36</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5856,23 +5918,23 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="6" t="s">
+      <c r="B55" s="14"/>
+      <c r="C55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>46275</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="5">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="5">
         <v>0.32</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <v>9.36</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5880,23 +5942,23 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="6" t="s">
+      <c r="B56" s="14"/>
+      <c r="C56" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>46276</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="5">
         <v>1.3759999999999999</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="5">
         <v>0.99</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="5">
         <v>9.2100000000000009</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5904,23 +5966,23 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="6" t="s">
+      <c r="B57" s="14"/>
+      <c r="C57" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="6">
         <v>46276</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="5">
         <v>1.468</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="5">
         <v>0.93</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="5">
         <v>8.94</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5928,23 +5990,23 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="6" t="s">
+      <c r="B58" s="14"/>
+      <c r="C58" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="6">
         <v>46276</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="5">
         <v>1.4419999999999999</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="5">
         <v>1.06</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="5">
         <v>9.25</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5952,25 +6014,25 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="15">
         <v>6</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="8">
         <v>46276</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="7">
         <v>0.28000000000000003</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="7">
         <v>7.41</v>
       </c>
-      <c r="H59" s="12" t="s">
+      <c r="H59" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5978,23 +6040,23 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="9" t="s">
+      <c r="B60" s="15"/>
+      <c r="C60" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D60" s="10">
+      <c r="D60" s="8">
         <v>46276</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="7">
         <v>0.23300000000000001</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="7">
         <v>0.66</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="7">
         <v>7.27</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="H60" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6002,23 +6064,23 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="9" t="s">
+      <c r="B61" s="15"/>
+      <c r="C61" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="8">
         <v>46276</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="7">
         <v>0.28199999999999997</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="7">
         <v>0.5</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="7">
         <v>8.1</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="H61" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6026,23 +6088,23 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="9" t="s">
+      <c r="B62" s="15"/>
+      <c r="C62" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="8">
         <v>46277</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="7">
         <v>0.27800000000000002</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="7">
         <v>0.54</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="7">
         <v>6.85</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6050,23 +6112,23 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="9" t="s">
+      <c r="B63" s="15"/>
+      <c r="C63" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="8">
         <v>46277</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="7">
         <v>0.313</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="7">
         <v>0.71</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="7">
         <v>6.29</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="H63" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6074,23 +6136,23 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="8"/>
-      <c r="C64" s="9" t="s">
+      <c r="B64" s="15"/>
+      <c r="C64" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="8">
         <v>46277</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="7">
         <v>0.32500000000000001</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="7">
         <v>0.41</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="7">
         <v>7.25</v>
       </c>
-      <c r="H64" s="12" t="s">
+      <c r="H64" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6098,25 +6160,25 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="14">
         <v>7</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="6">
         <v>46279</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="5">
         <v>0.72</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <v>8.7200000000000006</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6124,23 +6186,23 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="6" t="s">
+      <c r="B66" s="14"/>
+      <c r="C66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="6">
         <v>46279</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="5">
         <v>0.505</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <v>8.4</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6148,23 +6210,23 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="6" t="s">
+      <c r="B67" s="14"/>
+      <c r="C67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="6">
         <v>46279</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E67" s="5">
         <v>0.67100000000000004</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="5">
         <v>0.64</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="5">
         <v>8.67</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6172,23 +6234,23 @@
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6" t="s">
+      <c r="B68" s="14"/>
+      <c r="C68" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="6">
         <v>46280</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="5">
         <v>0.35</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="5">
         <v>0.49</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="5">
         <v>9.5299999999999994</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6196,23 +6258,23 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="6" t="s">
+      <c r="B69" s="14"/>
+      <c r="C69" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="6">
         <v>46280</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E69" s="5">
         <v>0.375</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69" s="5">
         <v>0.46</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G69" s="5">
         <v>9.86</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6220,23 +6282,23 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="6" t="s">
+      <c r="B70" s="14"/>
+      <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="6">
         <v>46280</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="5">
         <v>0.36899999999999999</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="5">
         <v>0.45</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G70" s="5">
         <v>9.32</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6244,23 +6306,23 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="6" t="s">
+      <c r="B71" s="14"/>
+      <c r="C71" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="6">
         <v>46280</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="5">
         <v>0.64</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G71" s="5">
         <v>11.12</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6268,23 +6330,23 @@
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="6" t="s">
+      <c r="B72" s="14"/>
+      <c r="C72" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="6">
         <v>46280</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="5">
         <v>0.58299999999999996</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="5">
         <v>0.53</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G72" s="5">
         <v>11.35</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6292,23 +6354,23 @@
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="6" t="s">
+      <c r="B73" s="14"/>
+      <c r="C73" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="6">
         <v>46280</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="5">
         <v>0.60699999999999998</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G73" s="5">
         <v>11.36</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6316,25 +6378,25 @@
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="15">
         <v>8</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="8">
         <v>46281</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="7">
         <v>0.44900000000000001</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="7">
         <v>0.63</v>
       </c>
-      <c r="G74" s="9">
+      <c r="G74" s="7">
         <v>11.56</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6342,23 +6404,23 @@
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="9" t="s">
+      <c r="B75" s="15"/>
+      <c r="C75" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="8">
         <v>46281</v>
       </c>
-      <c r="E75" s="9">
+      <c r="E75" s="7">
         <v>0.46800000000000003</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="7">
         <v>0.6</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="7">
         <v>11.66</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6366,23 +6428,23 @@
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="9" t="s">
+      <c r="B76" s="15"/>
+      <c r="C76" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D76" s="10">
+      <c r="D76" s="8">
         <v>46281</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="7">
         <v>0.438</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="7">
         <v>0.67</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="7">
         <v>11.67</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="H76" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6390,23 +6452,23 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="9" t="s">
+      <c r="B77" s="15"/>
+      <c r="C77" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="8">
         <v>46281</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="7">
         <v>0.59599999999999997</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="7">
         <v>0.59</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="7">
         <v>9.1300000000000008</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="H77" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6414,23 +6476,23 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="9" t="s">
+      <c r="B78" s="15"/>
+      <c r="C78" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D78" s="10">
+      <c r="D78" s="8">
         <v>46281</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="7">
         <v>0.58499999999999996</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="7">
         <v>9.2899999999999991</v>
       </c>
-      <c r="H78" s="12" t="s">
+      <c r="H78" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6438,23 +6500,23 @@
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="9" t="s">
+      <c r="B79" s="15"/>
+      <c r="C79" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D79" s="10">
+      <c r="D79" s="8">
         <v>46281</v>
       </c>
-      <c r="E79" s="9">
+      <c r="E79" s="7">
         <v>0.58299999999999996</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="7">
         <v>9.14</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="H79" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6462,23 +6524,23 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="9" t="s">
+      <c r="B80" s="15"/>
+      <c r="C80" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="8">
         <v>46282</v>
       </c>
-      <c r="E80" s="9">
+      <c r="E80" s="7">
         <v>0.57699999999999996</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="7">
         <v>0.53</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="7">
         <v>10.92</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="H80" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6486,23 +6548,23 @@
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="9" t="s">
+      <c r="B81" s="15"/>
+      <c r="C81" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D81" s="8">
         <v>46282</v>
       </c>
-      <c r="E81" s="9">
+      <c r="E81" s="7">
         <v>0.68</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81" s="7">
         <v>0.67</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="7">
         <v>10.54</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="H81" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6510,23 +6572,23 @@
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="9" t="s">
+      <c r="B82" s="15"/>
+      <c r="C82" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D82" s="10">
+      <c r="D82" s="8">
         <v>46282</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="7">
         <v>0.58599999999999997</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="7">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="7">
         <v>11.77</v>
       </c>
-      <c r="H82" s="12" t="s">
+      <c r="H82" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6534,23 +6596,23 @@
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="9" t="s">
+      <c r="B83" s="15"/>
+      <c r="C83" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83" s="8">
         <v>46282</v>
       </c>
-      <c r="E83" s="9">
+      <c r="E83" s="7">
         <v>0.73599999999999999</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="7">
         <v>0.61</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="7">
         <v>9.9</v>
       </c>
-      <c r="H83" s="12" t="s">
+      <c r="H83" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6558,23 +6620,23 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="9" t="s">
+      <c r="B84" s="15"/>
+      <c r="C84" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D84" s="10">
+      <c r="D84" s="8">
         <v>46282</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="7">
         <v>0.69099999999999995</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="7">
         <v>0.53</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="7">
         <v>10.31</v>
       </c>
-      <c r="H84" s="12" t="s">
+      <c r="H84" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6582,23 +6644,23 @@
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="9" t="s">
+      <c r="B85" s="15"/>
+      <c r="C85" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="8">
         <v>46282</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="7">
         <v>0.629</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="7">
         <v>0.51</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="7">
         <v>8.64</v>
       </c>
-      <c r="H85" s="12" t="s">
+      <c r="H85" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6606,25 +6668,25 @@
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B86" s="14">
         <v>9</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="6">
         <v>46283</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E86" s="5">
         <v>0.78200000000000003</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G86" s="5">
         <v>12.04</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6632,23 +6694,23 @@
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="6" t="s">
+      <c r="B87" s="14"/>
+      <c r="C87" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="6">
         <v>46283</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="5">
         <v>0.75900000000000001</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="5">
         <v>0.52</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="5">
         <v>12.08</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6656,23 +6718,23 @@
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="6" t="s">
+      <c r="B88" s="14"/>
+      <c r="C88" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="6">
         <v>46283</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E88" s="5">
         <v>0.76300000000000001</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="5">
         <v>0.54</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G88" s="5">
         <v>12.03</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6680,23 +6742,23 @@
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="6" t="s">
+      <c r="B89" s="14"/>
+      <c r="C89" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="6">
         <v>46283</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E89" s="5">
         <v>0.52500000000000002</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="5">
         <v>0.74</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G89" s="5">
         <v>11.56</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6704,23 +6766,23 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="6" t="s">
+      <c r="B90" s="14"/>
+      <c r="C90" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="6">
         <v>46283</v>
       </c>
-      <c r="E90" s="6">
+      <c r="E90" s="5">
         <v>0.55700000000000005</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="5">
         <v>0.72</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G90" s="5">
         <v>12.77</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6728,23 +6790,23 @@
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="6" t="s">
+      <c r="B91" s="14"/>
+      <c r="C91" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="6">
         <v>46283</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E91" s="5">
         <v>0.46800000000000003</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="5">
         <v>0.69</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G91" s="5">
         <v>9.9</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6752,23 +6814,23 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="6" t="s">
+      <c r="B92" s="14"/>
+      <c r="C92" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="6">
         <v>46284</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E92" s="5">
         <v>0.57099999999999995</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="5">
         <v>0.8</v>
       </c>
-      <c r="G92" s="6">
+      <c r="G92" s="5">
         <v>15.95</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6776,23 +6838,23 @@
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="6" t="s">
+      <c r="B93" s="14"/>
+      <c r="C93" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="6">
         <v>46284</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E93" s="5">
         <v>0.64400000000000002</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="5">
         <v>1.04</v>
       </c>
-      <c r="G93" s="6">
+      <c r="G93" s="5">
         <v>16.68</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6800,23 +6862,23 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="5"/>
-      <c r="C94" s="6" t="s">
+      <c r="B94" s="14"/>
+      <c r="C94" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="6">
         <v>46284</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E94" s="5">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="5">
         <v>1.06</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G94" s="5">
         <v>17.13</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6824,23 +6886,23 @@
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="6" t="s">
+      <c r="B95" s="14"/>
+      <c r="C95" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="6">
         <v>46284</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E95" s="5">
         <v>0.53100000000000003</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="5">
         <v>1.17</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G95" s="5">
         <v>19.079999999999998</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6848,23 +6910,23 @@
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="6" t="s">
+      <c r="B96" s="14"/>
+      <c r="C96" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="6">
         <v>46284</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E96" s="5">
         <v>0.60299999999999998</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="5">
         <v>1.39</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G96" s="5">
         <v>18.75</v>
       </c>
-      <c r="H96" s="11" t="s">
+      <c r="H96" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6872,23 +6934,23 @@
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="6" t="s">
+      <c r="B97" s="14"/>
+      <c r="C97" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="6">
         <v>46284</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E97" s="5">
         <v>0.50800000000000001</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="5">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G97" s="5">
         <v>18.14</v>
       </c>
-      <c r="H97" s="11" t="s">
+      <c r="H97" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6896,25 +6958,25 @@
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="15">
         <v>10</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="8">
         <v>46286</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="7">
         <v>1.046</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="7">
         <v>1.86</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="7">
         <v>19.690000000000001</v>
       </c>
-      <c r="H98" s="12" t="s">
+      <c r="H98" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6922,23 +6984,23 @@
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" s="8"/>
-      <c r="C99" s="9" t="s">
+      <c r="B99" s="15"/>
+      <c r="C99" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D99" s="10">
+      <c r="D99" s="8">
         <v>46286</v>
       </c>
-      <c r="E99" s="9">
+      <c r="E99" s="7">
         <v>0.94899999999999995</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="7">
         <v>1.98</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="7">
         <v>20.5</v>
       </c>
-      <c r="H99" s="12" t="s">
+      <c r="H99" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6946,23 +7008,23 @@
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="9" t="s">
+      <c r="B100" s="15"/>
+      <c r="C100" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="8">
         <v>46286</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="7">
         <v>0.96299999999999997</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="7">
         <v>2.13</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="7">
         <v>19.89</v>
       </c>
-      <c r="H100" s="12" t="s">
+      <c r="H100" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6970,23 +7032,23 @@
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" s="8"/>
-      <c r="C101" s="9" t="s">
+      <c r="B101" s="15"/>
+      <c r="C101" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D101" s="10">
+      <c r="D101" s="8">
         <v>46286</v>
       </c>
-      <c r="E101" s="9">
+      <c r="E101" s="7">
         <v>0.53800000000000003</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="7">
         <v>1.2</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="7">
         <v>18.95</v>
       </c>
-      <c r="H101" s="12" t="s">
+      <c r="H101" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6994,23 +7056,23 @@
       <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" s="8"/>
-      <c r="C102" s="9" t="s">
+      <c r="B102" s="15"/>
+      <c r="C102" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D102" s="10">
+      <c r="D102" s="8">
         <v>46286</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="7">
         <v>0.55600000000000005</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="7">
         <v>1.19</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="7">
         <v>18.75</v>
       </c>
-      <c r="H102" s="12" t="s">
+      <c r="H102" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7018,23 +7080,23 @@
       <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" s="8"/>
-      <c r="C103" s="9" t="s">
+      <c r="B103" s="15"/>
+      <c r="C103" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D103" s="10">
+      <c r="D103" s="8">
         <v>46286</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="7">
         <v>0.56599999999999995</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="7">
         <v>1.25</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="7">
         <v>18.899999999999999</v>
       </c>
-      <c r="H103" s="12" t="s">
+      <c r="H103" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7042,23 +7104,23 @@
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" s="8"/>
-      <c r="C104" s="9" t="s">
+      <c r="B104" s="15"/>
+      <c r="C104" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D104" s="10">
+      <c r="D104" s="8">
         <v>46287</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="7">
         <v>0.80600000000000005</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="7">
         <v>1.08</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="7">
         <v>19.71</v>
       </c>
-      <c r="H104" s="12" t="s">
+      <c r="H104" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7066,23 +7128,23 @@
       <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" s="8"/>
-      <c r="C105" s="9" t="s">
+      <c r="B105" s="15"/>
+      <c r="C105" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D105" s="10">
+      <c r="D105" s="8">
         <v>46287</v>
       </c>
-      <c r="E105" s="9">
+      <c r="E105" s="7">
         <v>0.81799999999999995</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105" s="7">
         <v>1.0900000000000001</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="7">
         <v>19.239999999999998</v>
       </c>
-      <c r="H105" s="12" t="s">
+      <c r="H105" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7090,23 +7152,23 @@
       <c r="A106">
         <v>105</v>
       </c>
-      <c r="B106" s="8"/>
-      <c r="C106" s="9" t="s">
+      <c r="B106" s="15"/>
+      <c r="C106" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D106" s="10">
+      <c r="D106" s="8">
         <v>46287</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E106" s="7">
         <v>0.85399999999999998</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="7">
         <v>1.1599999999999999</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="7">
         <v>19.87</v>
       </c>
-      <c r="H106" s="12" t="s">
+      <c r="H106" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7114,23 +7176,23 @@
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="8"/>
-      <c r="C107" s="9" t="s">
+      <c r="B107" s="15"/>
+      <c r="C107" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D107" s="10">
+      <c r="D107" s="8">
         <v>46287</v>
       </c>
-      <c r="E107" s="9">
+      <c r="E107" s="7">
         <v>0.75700000000000001</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="7">
         <v>1.07</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="7">
         <v>15.22</v>
       </c>
-      <c r="H107" s="12" t="s">
+      <c r="H107" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7138,23 +7200,23 @@
       <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" s="8"/>
-      <c r="C108" s="9" t="s">
+      <c r="B108" s="15"/>
+      <c r="C108" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D108" s="10">
+      <c r="D108" s="8">
         <v>46287</v>
       </c>
-      <c r="E108" s="9">
+      <c r="E108" s="7">
         <v>0.75</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="7">
         <v>1.05</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108" s="7">
         <v>15.65</v>
       </c>
-      <c r="H108" s="12" t="s">
+      <c r="H108" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7162,23 +7224,23 @@
       <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" s="8"/>
-      <c r="C109" s="9" t="s">
+      <c r="B109" s="15"/>
+      <c r="C109" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D109" s="10">
+      <c r="D109" s="8">
         <v>46287</v>
       </c>
-      <c r="E109" s="9">
+      <c r="E109" s="7">
         <v>0.74</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="7">
         <v>1.08</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="7">
         <v>15.65</v>
       </c>
-      <c r="H109" s="12" t="s">
+      <c r="H109" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7186,23 +7248,23 @@
       <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" s="8"/>
-      <c r="C110" s="9" t="s">
+      <c r="B110" s="15"/>
+      <c r="C110" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D110" s="10">
+      <c r="D110" s="8">
         <v>46288</v>
       </c>
-      <c r="E110" s="9">
+      <c r="E110" s="7">
         <v>1.0669999999999999</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="7">
         <v>0.94</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="7">
         <v>18.3</v>
       </c>
-      <c r="H110" s="12" t="s">
+      <c r="H110" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7210,23 +7272,23 @@
       <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" s="8"/>
-      <c r="C111" s="9" t="s">
+      <c r="B111" s="15"/>
+      <c r="C111" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D111" s="10">
+      <c r="D111" s="8">
         <v>46288</v>
       </c>
-      <c r="E111" s="9">
+      <c r="E111" s="7">
         <v>1.022</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="7">
         <v>0.94</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="7">
         <v>17.97</v>
       </c>
-      <c r="H111" s="12" t="s">
+      <c r="H111" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7234,23 +7296,23 @@
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" s="8"/>
-      <c r="C112" s="9" t="s">
+      <c r="B112" s="15"/>
+      <c r="C112" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D112" s="10">
+      <c r="D112" s="8">
         <v>46288</v>
       </c>
-      <c r="E112" s="9">
+      <c r="E112" s="7">
         <v>1.0740000000000001</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112" s="7">
         <v>0.92</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="7">
         <v>17.87</v>
       </c>
-      <c r="H112" s="12" t="s">
+      <c r="H112" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7258,23 +7320,23 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" s="8"/>
-      <c r="C113" s="9" t="s">
+      <c r="B113" s="15"/>
+      <c r="C113" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D113" s="10">
+      <c r="D113" s="8">
         <v>46288</v>
       </c>
-      <c r="E113" s="9">
+      <c r="E113" s="7">
         <v>0.71299999999999997</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="7">
         <v>0.64</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113" s="7">
         <v>16.61</v>
       </c>
-      <c r="H113" s="12" t="s">
+      <c r="H113" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7282,23 +7344,23 @@
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" s="8"/>
-      <c r="C114" s="9" t="s">
+      <c r="B114" s="15"/>
+      <c r="C114" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D114" s="10">
+      <c r="D114" s="8">
         <v>46288</v>
       </c>
-      <c r="E114" s="9">
+      <c r="E114" s="7">
         <v>0.745</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114" s="7">
         <v>0.61</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="7">
         <v>16.53</v>
       </c>
-      <c r="H114" s="12" t="s">
+      <c r="H114" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7306,23 +7368,23 @@
       <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" s="8"/>
-      <c r="C115" s="9" t="s">
+      <c r="B115" s="15"/>
+      <c r="C115" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D115" s="10">
+      <c r="D115" s="8">
         <v>46288</v>
       </c>
-      <c r="E115" s="9">
+      <c r="E115" s="7">
         <v>0.747</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115" s="7">
         <v>0.69</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="7">
         <v>16.399999999999999</v>
       </c>
-      <c r="H115" s="12" t="s">
+      <c r="H115" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7330,23 +7392,23 @@
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" s="8"/>
-      <c r="C116" s="9" t="s">
+      <c r="B116" s="15"/>
+      <c r="C116" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D116" s="10">
+      <c r="D116" s="8">
         <v>46289</v>
       </c>
-      <c r="E116" s="9">
+      <c r="E116" s="7">
         <v>0.86099999999999999</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116" s="7">
         <v>1.02</v>
       </c>
-      <c r="G116" s="9">
+      <c r="G116" s="7">
         <v>16.37</v>
       </c>
-      <c r="H116" s="12" t="s">
+      <c r="H116" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7354,23 +7416,23 @@
       <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" s="8"/>
-      <c r="C117" s="9" t="s">
+      <c r="B117" s="15"/>
+      <c r="C117" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D117" s="10">
+      <c r="D117" s="8">
         <v>46289</v>
       </c>
-      <c r="E117" s="9">
+      <c r="E117" s="7">
         <v>0.90500000000000003</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117" s="7">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117" s="7">
         <v>16.22</v>
       </c>
-      <c r="H117" s="12" t="s">
+      <c r="H117" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7378,23 +7440,23 @@
       <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" s="8"/>
-      <c r="C118" s="9" t="s">
+      <c r="B118" s="15"/>
+      <c r="C118" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D118" s="10">
+      <c r="D118" s="8">
         <v>46289</v>
       </c>
-      <c r="E118" s="9">
+      <c r="E118" s="7">
         <v>0.86699999999999999</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F118" s="7">
         <v>0.88</v>
       </c>
-      <c r="G118" s="9">
+      <c r="G118" s="7">
         <v>17.47</v>
       </c>
-      <c r="H118" s="12" t="s">
+      <c r="H118" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7402,25 +7464,25 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" s="5">
+      <c r="B119" s="14">
         <v>11</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="6">
         <v>46289</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E119" s="5">
         <v>0.57699999999999996</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="5">
         <v>1.87</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G119" s="5">
         <v>17.46</v>
       </c>
-      <c r="H119" s="11" t="s">
+      <c r="H119" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7428,23 +7490,23 @@
       <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" s="5"/>
-      <c r="C120" s="6" t="s">
+      <c r="B120" s="14"/>
+      <c r="C120" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D120" s="7">
+      <c r="D120" s="6">
         <v>46289</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E120" s="5">
         <v>0.59699999999999998</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="5">
         <v>1.8</v>
       </c>
-      <c r="G120" s="6">
+      <c r="G120" s="5">
         <v>17.75</v>
       </c>
-      <c r="H120" s="11" t="s">
+      <c r="H120" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7452,23 +7514,23 @@
       <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" s="5"/>
-      <c r="C121" s="6" t="s">
+      <c r="B121" s="14"/>
+      <c r="C121" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D121" s="7">
+      <c r="D121" s="6">
         <v>46289</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="5">
         <v>0.56499999999999995</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="5">
         <v>1.89</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="5">
         <v>17.72</v>
       </c>
-      <c r="H121" s="11" t="s">
+      <c r="H121" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7476,23 +7538,23 @@
       <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="6" t="s">
+      <c r="B122" s="14"/>
+      <c r="C122" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D122" s="7">
+      <c r="D122" s="6">
         <v>46290</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="5">
         <v>0.75</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="5">
         <v>1.24</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="5">
         <v>20.04</v>
       </c>
-      <c r="H122" s="11" t="s">
+      <c r="H122" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7500,23 +7562,23 @@
       <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="6" t="s">
+      <c r="B123" s="14"/>
+      <c r="C123" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D123" s="7">
+      <c r="D123" s="6">
         <v>46290</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="5">
         <v>0.71199999999999997</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="5">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G123" s="5">
         <v>19.91</v>
       </c>
-      <c r="H123" s="11" t="s">
+      <c r="H123" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7524,23 +7586,23 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="6" t="s">
+      <c r="B124" s="14"/>
+      <c r="C124" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D124" s="6">
         <v>46290</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E124" s="5">
         <v>0.72799999999999998</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124" s="5">
         <v>1.29</v>
       </c>
-      <c r="G124" s="6">
+      <c r="G124" s="5">
         <v>20.12</v>
       </c>
-      <c r="H124" s="11" t="s">
+      <c r="H124" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7548,17 +7610,17 @@
       <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" s="5"/>
-      <c r="C125" s="6" t="s">
+      <c r="B125" s="14"/>
+      <c r="C125" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="6">
         <v>46290</v>
       </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="11" t="s">
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7566,17 +7628,17 @@
       <c r="A126">
         <v>125</v>
       </c>
-      <c r="B126" s="5"/>
-      <c r="C126" s="6" t="s">
+      <c r="B126" s="14"/>
+      <c r="C126" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="6">
         <v>46290</v>
       </c>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="11" t="s">
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7584,17 +7646,17 @@
       <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" s="5"/>
-      <c r="C127" s="6" t="s">
+      <c r="B127" s="14"/>
+      <c r="C127" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D127" s="7">
+      <c r="D127" s="6">
         <v>46290</v>
       </c>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="11" t="s">
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7602,25 +7664,25 @@
       <c r="A128">
         <v>127</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="15">
         <v>12</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D128" s="10">
+      <c r="D128" s="8">
         <v>46292</v>
       </c>
-      <c r="E128" s="9">
+      <c r="E128" s="7">
         <v>0.52700000000000002</v>
       </c>
-      <c r="F128" s="9">
+      <c r="F128" s="7">
         <v>1.1599999999999999</v>
       </c>
-      <c r="G128" s="9">
+      <c r="G128" s="7">
         <v>13.75</v>
       </c>
-      <c r="H128" s="12" t="s">
+      <c r="H128" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7628,23 +7690,23 @@
       <c r="A129">
         <v>128</v>
       </c>
-      <c r="B129" s="8"/>
-      <c r="C129" s="9" t="s">
+      <c r="B129" s="15"/>
+      <c r="C129" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D129" s="10">
+      <c r="D129" s="8">
         <v>46292</v>
       </c>
-      <c r="E129" s="9">
+      <c r="E129" s="7">
         <v>0.51100000000000001</v>
       </c>
-      <c r="F129" s="9">
+      <c r="F129" s="7">
         <v>1.07</v>
       </c>
-      <c r="G129" s="9">
+      <c r="G129" s="7">
         <v>13.27</v>
       </c>
-      <c r="H129" s="12" t="s">
+      <c r="H129" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7652,23 +7714,23 @@
       <c r="A130">
         <v>129</v>
       </c>
-      <c r="B130" s="8"/>
-      <c r="C130" s="9" t="s">
+      <c r="B130" s="15"/>
+      <c r="C130" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D130" s="10">
+      <c r="D130" s="8">
         <v>46292</v>
       </c>
-      <c r="E130" s="9">
+      <c r="E130" s="7">
         <v>0.52300000000000002</v>
       </c>
-      <c r="F130" s="9">
+      <c r="F130" s="7">
         <v>1.08</v>
       </c>
-      <c r="G130" s="9">
+      <c r="G130" s="7">
         <v>13.91</v>
       </c>
-      <c r="H130" s="12" t="s">
+      <c r="H130" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7676,23 +7738,23 @@
       <c r="A131">
         <v>130</v>
       </c>
-      <c r="B131" s="8"/>
-      <c r="C131" s="9" t="s">
+      <c r="B131" s="15"/>
+      <c r="C131" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D131" s="10">
+      <c r="D131" s="8">
         <v>46292</v>
       </c>
-      <c r="E131" s="9">
+      <c r="E131" s="7">
         <v>0.76</v>
       </c>
-      <c r="F131" s="9">
+      <c r="F131" s="7">
         <v>1.44</v>
       </c>
-      <c r="G131" s="9">
+      <c r="G131" s="7">
         <v>15.45</v>
       </c>
-      <c r="H131" s="12" t="s">
+      <c r="H131" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7700,23 +7762,23 @@
       <c r="A132">
         <v>131</v>
       </c>
-      <c r="B132" s="8"/>
-      <c r="C132" s="9" t="s">
+      <c r="B132" s="15"/>
+      <c r="C132" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D132" s="10">
+      <c r="D132" s="8">
         <v>46292</v>
       </c>
-      <c r="E132" s="9">
+      <c r="E132" s="7">
         <v>0.73199999999999998</v>
       </c>
-      <c r="F132" s="9">
+      <c r="F132" s="7">
         <v>1.43</v>
       </c>
-      <c r="G132" s="9">
+      <c r="G132" s="7">
         <v>15.47</v>
       </c>
-      <c r="H132" s="12" t="s">
+      <c r="H132" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7724,23 +7786,23 @@
       <c r="A133">
         <v>132</v>
       </c>
-      <c r="B133" s="8"/>
-      <c r="C133" s="9" t="s">
+      <c r="B133" s="15"/>
+      <c r="C133" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D133" s="10">
+      <c r="D133" s="8">
         <v>46292</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="7">
         <v>0.751</v>
       </c>
-      <c r="F133" s="9">
+      <c r="F133" s="7">
         <v>1.45</v>
       </c>
-      <c r="G133" s="9">
+      <c r="G133" s="7">
         <v>15.17</v>
       </c>
-      <c r="H133" s="12" t="s">
+      <c r="H133" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7748,23 +7810,23 @@
       <c r="A134">
         <v>133</v>
       </c>
-      <c r="B134" s="8"/>
-      <c r="C134" s="9" t="s">
+      <c r="B134" s="15"/>
+      <c r="C134" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D134" s="10">
+      <c r="D134" s="8">
         <v>46293</v>
       </c>
-      <c r="E134" s="9">
+      <c r="E134" s="7">
         <v>0.58799999999999997</v>
       </c>
-      <c r="F134" s="9">
+      <c r="F134" s="7">
         <v>1.07</v>
       </c>
-      <c r="G134" s="9">
+      <c r="G134" s="7">
         <v>14.31</v>
       </c>
-      <c r="H134" s="12" t="s">
+      <c r="H134" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7772,23 +7834,23 @@
       <c r="A135">
         <v>134</v>
       </c>
-      <c r="B135" s="8"/>
-      <c r="C135" s="9" t="s">
+      <c r="B135" s="15"/>
+      <c r="C135" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D135" s="10">
+      <c r="D135" s="8">
         <v>46293</v>
       </c>
-      <c r="E135" s="9">
+      <c r="E135" s="7">
         <v>0.57199999999999995</v>
       </c>
-      <c r="F135" s="9">
+      <c r="F135" s="7">
         <v>1.18</v>
       </c>
-      <c r="G135" s="9">
+      <c r="G135" s="7">
         <v>14.17</v>
       </c>
-      <c r="H135" s="12" t="s">
+      <c r="H135" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7796,23 +7858,23 @@
       <c r="A136">
         <v>135</v>
       </c>
-      <c r="B136" s="8"/>
-      <c r="C136" s="9" t="s">
+      <c r="B136" s="15"/>
+      <c r="C136" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D136" s="10">
+      <c r="D136" s="8">
         <v>46293</v>
       </c>
-      <c r="E136" s="9">
+      <c r="E136" s="7">
         <v>0.59499999999999997</v>
       </c>
-      <c r="F136" s="9">
+      <c r="F136" s="7">
         <v>1.05</v>
       </c>
-      <c r="G136" s="9">
+      <c r="G136" s="7">
         <v>14.35</v>
       </c>
-      <c r="H136" s="12" t="s">
+      <c r="H136" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7820,23 +7882,23 @@
       <c r="A137">
         <v>136</v>
       </c>
-      <c r="B137" s="8"/>
-      <c r="C137" s="9" t="s">
+      <c r="B137" s="15"/>
+      <c r="C137" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D137" s="10">
+      <c r="D137" s="8">
         <v>46293</v>
       </c>
-      <c r="E137" s="9">
+      <c r="E137" s="7">
         <v>0.53200000000000003</v>
       </c>
-      <c r="F137" s="9">
+      <c r="F137" s="7">
         <v>2.09</v>
       </c>
-      <c r="G137" s="9">
+      <c r="G137" s="7">
         <v>17.87</v>
       </c>
-      <c r="H137" s="12" t="s">
+      <c r="H137" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7844,23 +7906,23 @@
       <c r="A138">
         <v>137</v>
       </c>
-      <c r="B138" s="8"/>
-      <c r="C138" s="9" t="s">
+      <c r="B138" s="15"/>
+      <c r="C138" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D138" s="10">
+      <c r="D138" s="8">
         <v>46293</v>
       </c>
-      <c r="E138" s="9">
+      <c r="E138" s="7">
         <v>0.57899999999999996</v>
       </c>
-      <c r="F138" s="9">
+      <c r="F138" s="7">
         <v>2.0299999999999998</v>
       </c>
-      <c r="G138" s="9">
+      <c r="G138" s="7">
         <v>17.97</v>
       </c>
-      <c r="H138" s="12" t="s">
+      <c r="H138" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7868,23 +7930,23 @@
       <c r="A139">
         <v>138</v>
       </c>
-      <c r="B139" s="8"/>
-      <c r="C139" s="9" t="s">
+      <c r="B139" s="15"/>
+      <c r="C139" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D139" s="10">
+      <c r="D139" s="8">
         <v>46293</v>
       </c>
-      <c r="E139" s="9">
+      <c r="E139" s="7">
         <v>0.53500000000000003</v>
       </c>
-      <c r="F139" s="9">
+      <c r="F139" s="7">
         <v>2.12</v>
       </c>
-      <c r="G139" s="9">
+      <c r="G139" s="7">
         <v>17.87</v>
       </c>
-      <c r="H139" s="12" t="s">
+      <c r="H139" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7892,23 +7954,23 @@
       <c r="A140">
         <v>139</v>
       </c>
-      <c r="B140" s="8"/>
-      <c r="C140" s="9" t="s">
+      <c r="B140" s="15"/>
+      <c r="C140" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D140" s="10">
+      <c r="D140" s="8">
         <v>46294</v>
       </c>
-      <c r="E140" s="9">
+      <c r="E140" s="7">
         <v>0.58299999999999996</v>
       </c>
-      <c r="F140" s="9">
+      <c r="F140" s="7">
         <v>1.07</v>
       </c>
-      <c r="G140" s="9">
+      <c r="G140" s="7">
         <v>19.14</v>
       </c>
-      <c r="H140" s="12" t="s">
+      <c r="H140" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7916,23 +7978,23 @@
       <c r="A141">
         <v>140</v>
       </c>
-      <c r="B141" s="8"/>
-      <c r="C141" s="9" t="s">
+      <c r="B141" s="15"/>
+      <c r="C141" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D141" s="10">
+      <c r="D141" s="8">
         <v>46294</v>
       </c>
-      <c r="E141" s="9">
+      <c r="E141" s="7">
         <v>0.54400000000000004</v>
       </c>
-      <c r="F141" s="9">
+      <c r="F141" s="7">
         <v>1.18</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G141" s="7">
         <v>18.68</v>
       </c>
-      <c r="H141" s="12" t="s">
+      <c r="H141" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7940,23 +8002,23 @@
       <c r="A142">
         <v>141</v>
       </c>
-      <c r="B142" s="8"/>
-      <c r="C142" s="9" t="s">
+      <c r="B142" s="15"/>
+      <c r="C142" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D142" s="10">
+      <c r="D142" s="8">
         <v>46294</v>
       </c>
-      <c r="E142" s="9">
+      <c r="E142" s="7">
         <v>0.52300000000000002</v>
       </c>
-      <c r="F142" s="9">
+      <c r="F142" s="7">
         <v>1.05</v>
       </c>
-      <c r="G142" s="9">
+      <c r="G142" s="7">
         <v>18.850000000000001</v>
       </c>
-      <c r="H142" s="12" t="s">
+      <c r="H142" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7964,23 +8026,23 @@
       <c r="A143">
         <v>142</v>
       </c>
-      <c r="B143" s="8"/>
-      <c r="C143" s="9" t="s">
+      <c r="B143" s="15"/>
+      <c r="C143" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D143" s="10">
+      <c r="D143" s="8">
         <v>46294</v>
       </c>
-      <c r="E143" s="9">
+      <c r="E143" s="7">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F143" s="9">
+      <c r="F143" s="7">
         <v>1.28</v>
       </c>
-      <c r="G143" s="9">
+      <c r="G143" s="7">
         <v>19.61</v>
       </c>
-      <c r="H143" s="12" t="s">
+      <c r="H143" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7988,23 +8050,23 @@
       <c r="A144">
         <v>143</v>
       </c>
-      <c r="B144" s="8"/>
-      <c r="C144" s="9" t="s">
+      <c r="B144" s="15"/>
+      <c r="C144" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D144" s="10">
+      <c r="D144" s="8">
         <v>46294</v>
       </c>
-      <c r="E144" s="9">
+      <c r="E144" s="7">
         <v>0.57499999999999996</v>
       </c>
-      <c r="F144" s="9">
+      <c r="F144" s="7">
         <v>1.23</v>
       </c>
-      <c r="G144" s="9">
+      <c r="G144" s="7">
         <v>19.61</v>
       </c>
-      <c r="H144" s="12" t="s">
+      <c r="H144" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8012,23 +8074,23 @@
       <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" s="8"/>
-      <c r="C145" s="9" t="s">
+      <c r="B145" s="15"/>
+      <c r="C145" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D145" s="10">
+      <c r="D145" s="8">
         <v>46294</v>
       </c>
-      <c r="E145" s="9">
+      <c r="E145" s="7">
         <v>0.50600000000000001</v>
       </c>
-      <c r="F145" s="9">
+      <c r="F145" s="7">
         <v>1.28</v>
       </c>
-      <c r="G145" s="9">
+      <c r="G145" s="7">
         <v>19.079999999999998</v>
       </c>
-      <c r="H145" s="12" t="s">
+      <c r="H145" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8036,25 +8098,25 @@
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" s="5">
+      <c r="B146" s="14">
         <v>13</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C146" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D146" s="7">
+      <c r="D146" s="6">
         <v>46294</v>
       </c>
-      <c r="E146" s="6">
+      <c r="E146" s="5">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="5">
         <v>1.42</v>
       </c>
-      <c r="G146" s="6">
+      <c r="G146" s="5">
         <v>19.61</v>
       </c>
-      <c r="H146" s="11" t="s">
+      <c r="H146" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8062,23 +8124,23 @@
       <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" s="5"/>
-      <c r="C147" s="6" t="s">
+      <c r="B147" s="14"/>
+      <c r="C147" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D147" s="7">
+      <c r="D147" s="6">
         <v>46294</v>
       </c>
-      <c r="E147" s="6">
+      <c r="E147" s="5">
         <v>0.57499999999999996</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="5">
         <v>1.39</v>
       </c>
-      <c r="G147" s="6">
+      <c r="G147" s="5">
         <v>19.61</v>
       </c>
-      <c r="H147" s="11" t="s">
+      <c r="H147" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8086,23 +8148,23 @@
       <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" s="5"/>
-      <c r="C148" s="6" t="s">
+      <c r="B148" s="14"/>
+      <c r="C148" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D148" s="7">
+      <c r="D148" s="6">
         <v>46294</v>
       </c>
-      <c r="E148" s="6">
+      <c r="E148" s="5">
         <v>0.50600000000000001</v>
       </c>
-      <c r="F148" s="6">
+      <c r="F148" s="5">
         <v>1.36</v>
       </c>
-      <c r="G148" s="6">
+      <c r="G148" s="5">
         <v>19.079999999999998</v>
       </c>
-      <c r="H148" s="11" t="s">
+      <c r="H148" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8110,23 +8172,23 @@
       <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="6" t="s">
+      <c r="B149" s="14"/>
+      <c r="C149" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D149" s="7">
+      <c r="D149" s="6">
         <v>46299</v>
       </c>
-      <c r="E149" s="6">
+      <c r="E149" s="5">
         <v>0.63</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F149" s="5">
         <v>0.66</v>
       </c>
-      <c r="G149" s="6">
+      <c r="G149" s="5">
         <v>16.059999999999999</v>
       </c>
-      <c r="H149" s="11" t="s">
+      <c r="H149" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8134,23 +8196,23 @@
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" s="5"/>
-      <c r="C150" s="6" t="s">
+      <c r="B150" s="14"/>
+      <c r="C150" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D150" s="7">
+      <c r="D150" s="6">
         <v>46299</v>
       </c>
-      <c r="E150" s="6">
+      <c r="E150" s="5">
         <v>0.46400000000000002</v>
       </c>
-      <c r="F150" s="6">
+      <c r="F150" s="5">
         <v>0.46</v>
       </c>
-      <c r="G150" s="6">
+      <c r="G150" s="5">
         <v>14.86</v>
       </c>
-      <c r="H150" s="11" t="s">
+      <c r="H150" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8158,23 +8220,23 @@
       <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" s="5"/>
-      <c r="C151" s="6" t="s">
+      <c r="B151" s="14"/>
+      <c r="C151" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D151" s="7">
+      <c r="D151" s="6">
         <v>46299</v>
       </c>
-      <c r="E151" s="6">
+      <c r="E151" s="5">
         <v>0.495</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F151" s="5">
         <v>0.4</v>
       </c>
-      <c r="G151" s="6">
+      <c r="G151" s="5">
         <v>16.149999999999999</v>
       </c>
-      <c r="H151" s="11" t="s">
+      <c r="H151" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8182,23 +8244,23 @@
       <c r="A152">
         <v>151</v>
       </c>
-      <c r="B152" s="5"/>
-      <c r="C152" s="6" t="s">
+      <c r="B152" s="14"/>
+      <c r="C152" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D152" s="7">
+      <c r="D152" s="6">
         <v>46299</v>
       </c>
-      <c r="E152" s="6">
+      <c r="E152" s="5">
         <v>0.443</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="5">
         <v>0.90800000000000003</v>
       </c>
-      <c r="G152" s="6">
+      <c r="G152" s="5">
         <v>27.297000000000001</v>
       </c>
-      <c r="H152" s="11" t="s">
+      <c r="H152" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8206,23 +8268,23 @@
       <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" s="5"/>
-      <c r="C153" s="6" t="s">
+      <c r="B153" s="14"/>
+      <c r="C153" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D153" s="7">
+      <c r="D153" s="6">
         <v>46299</v>
       </c>
-      <c r="E153" s="6">
+      <c r="E153" s="5">
         <v>0.35899999999999999</v>
       </c>
-      <c r="F153" s="6">
+      <c r="F153" s="5">
         <v>0.94099999999999995</v>
       </c>
-      <c r="G153" s="6">
+      <c r="G153" s="5">
         <v>27.939</v>
       </c>
-      <c r="H153" s="11" t="s">
+      <c r="H153" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8230,23 +8292,23 @@
       <c r="A154">
         <v>153</v>
       </c>
-      <c r="B154" s="5"/>
-      <c r="C154" s="6" t="s">
+      <c r="B154" s="14"/>
+      <c r="C154" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D154" s="7">
+      <c r="D154" s="6">
         <v>46299</v>
       </c>
-      <c r="E154" s="6">
+      <c r="E154" s="5">
         <v>0.34100000000000003</v>
       </c>
-      <c r="F154" s="6">
+      <c r="F154" s="5">
         <v>1.216</v>
       </c>
-      <c r="G154" s="6">
+      <c r="G154" s="5">
         <v>27.788</v>
       </c>
-      <c r="H154" s="11" t="s">
+      <c r="H154" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8254,23 +8316,23 @@
       <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" s="5"/>
-      <c r="C155" s="6" t="s">
+      <c r="B155" s="14"/>
+      <c r="C155" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D155" s="7">
+      <c r="D155" s="6">
         <v>46300</v>
       </c>
-      <c r="E155" s="6">
+      <c r="E155" s="5">
         <v>0.66100000000000003</v>
       </c>
-      <c r="F155" s="6">
+      <c r="F155" s="5">
         <v>0.73</v>
       </c>
-      <c r="G155" s="6">
+      <c r="G155" s="5">
         <v>19.12</v>
       </c>
-      <c r="H155" s="11" t="s">
+      <c r="H155" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I155" t="e" cm="1">
@@ -8282,23 +8344,23 @@
       <c r="A156">
         <v>155</v>
       </c>
-      <c r="B156" s="5"/>
-      <c r="C156" s="6" t="s">
+      <c r="B156" s="14"/>
+      <c r="C156" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D156" s="7">
+      <c r="D156" s="6">
         <v>46300</v>
       </c>
-      <c r="E156" s="6">
+      <c r="E156" s="5">
         <v>0.628</v>
       </c>
-      <c r="F156" s="6">
+      <c r="F156" s="5">
         <v>0.72</v>
       </c>
-      <c r="G156" s="6">
+      <c r="G156" s="5">
         <v>19.23</v>
       </c>
-      <c r="H156" s="11" t="s">
+      <c r="H156" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8306,23 +8368,23 @@
       <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6" t="s">
+      <c r="B157" s="14"/>
+      <c r="C157" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D157" s="7">
+      <c r="D157" s="6">
         <v>46300</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E157" s="5">
         <v>0.63600000000000001</v>
       </c>
-      <c r="F157" s="6">
+      <c r="F157" s="5">
         <v>0.73</v>
       </c>
-      <c r="G157" s="6">
+      <c r="G157" s="5">
         <v>19.16</v>
       </c>
-      <c r="H157" s="11" t="s">
+      <c r="H157" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8330,23 +8392,23 @@
       <c r="A158">
         <v>157</v>
       </c>
-      <c r="B158" s="5"/>
-      <c r="C158" s="6" t="s">
+      <c r="B158" s="14"/>
+      <c r="C158" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D158" s="7">
+      <c r="D158" s="6">
         <v>46300</v>
       </c>
-      <c r="E158" s="6">
+      <c r="E158" s="5">
         <v>0.498</v>
       </c>
-      <c r="F158" s="6">
+      <c r="F158" s="5">
         <v>1.1399999999999999</v>
       </c>
-      <c r="G158" s="6">
+      <c r="G158" s="5">
         <v>19.010000000000002</v>
       </c>
-      <c r="H158" s="11" t="s">
+      <c r="H158" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8354,23 +8416,23 @@
       <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" s="5"/>
-      <c r="C159" s="6" t="s">
+      <c r="B159" s="14"/>
+      <c r="C159" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D159" s="7">
+      <c r="D159" s="6">
         <v>46300</v>
       </c>
-      <c r="E159" s="6">
+      <c r="E159" s="5">
         <v>0.57399999999999995</v>
       </c>
-      <c r="F159" s="6">
+      <c r="F159" s="5">
         <v>0.84</v>
       </c>
-      <c r="G159" s="6">
+      <c r="G159" s="5">
         <v>19.079999999999998</v>
       </c>
-      <c r="H159" s="11" t="s">
+      <c r="H159" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8378,23 +8440,23 @@
       <c r="A160">
         <v>159</v>
       </c>
-      <c r="B160" s="5"/>
-      <c r="C160" s="6" t="s">
+      <c r="B160" s="14"/>
+      <c r="C160" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D160" s="7">
+      <c r="D160" s="6">
         <v>46300</v>
       </c>
-      <c r="E160" s="6">
+      <c r="E160" s="5">
         <v>0.55600000000000005</v>
       </c>
-      <c r="F160" s="6">
+      <c r="F160" s="5">
         <v>0.77</v>
       </c>
-      <c r="G160" s="6">
+      <c r="G160" s="5">
         <v>18.190000000000001</v>
       </c>
-      <c r="H160" s="11" t="s">
+      <c r="H160" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8402,25 +8464,25 @@
       <c r="A161">
         <v>160</v>
       </c>
-      <c r="B161" s="8">
+      <c r="B161" s="15">
         <v>14</v>
       </c>
-      <c r="C161" s="9" t="s">
+      <c r="C161" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D161" s="10">
+      <c r="D161" s="8">
         <v>46302</v>
       </c>
-      <c r="E161" s="9">
+      <c r="E161" s="7">
         <v>0.314</v>
       </c>
-      <c r="F161" s="9">
+      <c r="F161" s="7">
         <v>0.08</v>
       </c>
-      <c r="G161" s="9">
+      <c r="G161" s="7">
         <v>7.89</v>
       </c>
-      <c r="H161" s="12" t="s">
+      <c r="H161" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8428,23 +8490,23 @@
       <c r="A162">
         <v>161</v>
       </c>
-      <c r="B162" s="8"/>
-      <c r="C162" s="9" t="s">
+      <c r="B162" s="15"/>
+      <c r="C162" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D162" s="10">
+      <c r="D162" s="8">
         <v>46302</v>
       </c>
-      <c r="E162" s="9">
+      <c r="E162" s="7">
         <v>0.32</v>
       </c>
-      <c r="F162" s="9">
+      <c r="F162" s="7">
         <v>0.01</v>
       </c>
-      <c r="G162" s="9">
+      <c r="G162" s="7">
         <v>7.64</v>
       </c>
-      <c r="H162" s="12" t="s">
+      <c r="H162" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8452,23 +8514,23 @@
       <c r="A163">
         <v>162</v>
       </c>
-      <c r="B163" s="8"/>
-      <c r="C163" s="9" t="s">
+      <c r="B163" s="15"/>
+      <c r="C163" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D163" s="10">
+      <c r="D163" s="8">
         <v>46302</v>
       </c>
-      <c r="E163" s="9">
+      <c r="E163" s="7">
         <v>0.32900000000000001</v>
       </c>
-      <c r="F163" s="9">
+      <c r="F163" s="7">
         <v>0.02</v>
       </c>
-      <c r="G163" s="9">
+      <c r="G163" s="7">
         <v>7.97</v>
       </c>
-      <c r="H163" s="12" t="s">
+      <c r="H163" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8476,23 +8538,23 @@
       <c r="A164">
         <v>163</v>
       </c>
-      <c r="B164" s="8"/>
-      <c r="C164" s="9" t="s">
+      <c r="B164" s="15"/>
+      <c r="C164" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D164" s="10">
+      <c r="D164" s="8">
         <v>46302</v>
       </c>
-      <c r="E164" s="9">
+      <c r="E164" s="7">
         <v>0.50800000000000001</v>
       </c>
-      <c r="F164" s="9">
+      <c r="F164" s="7">
         <v>0.18</v>
       </c>
-      <c r="G164" s="9">
+      <c r="G164" s="7">
         <v>9.59</v>
       </c>
-      <c r="H164" s="12" t="s">
+      <c r="H164" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8500,23 +8562,23 @@
       <c r="A165">
         <v>164</v>
       </c>
-      <c r="B165" s="8"/>
-      <c r="C165" s="9" t="s">
+      <c r="B165" s="15"/>
+      <c r="C165" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D165" s="10">
+      <c r="D165" s="8">
         <v>46302</v>
       </c>
-      <c r="E165" s="9">
+      <c r="E165" s="7">
         <v>0.41099999999999998</v>
       </c>
-      <c r="F165" s="9">
+      <c r="F165" s="7">
         <v>10.11</v>
       </c>
-      <c r="G165" s="9">
+      <c r="G165" s="7">
         <v>10.11</v>
       </c>
-      <c r="H165" s="12" t="s">
+      <c r="H165" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8524,23 +8586,23 @@
       <c r="A166">
         <v>165</v>
       </c>
-      <c r="B166" s="8"/>
-      <c r="C166" s="9" t="s">
+      <c r="B166" s="15"/>
+      <c r="C166" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D166" s="10">
+      <c r="D166" s="8">
         <v>46302</v>
       </c>
-      <c r="E166" s="9">
+      <c r="E166" s="7">
         <v>0.504</v>
       </c>
-      <c r="F166" s="9">
+      <c r="F166" s="7">
         <v>9.74</v>
       </c>
-      <c r="G166" s="9">
+      <c r="G166" s="7">
         <v>9.74</v>
       </c>
-      <c r="H166" s="12" t="s">
+      <c r="H166" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8548,23 +8610,23 @@
       <c r="A167">
         <v>166</v>
       </c>
-      <c r="B167" s="8"/>
-      <c r="C167" s="9" t="s">
+      <c r="B167" s="15"/>
+      <c r="C167" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D167" s="10">
+      <c r="D167" s="8">
         <v>46303</v>
       </c>
-      <c r="E167" s="9">
+      <c r="E167" s="7">
         <v>0.42199999999999999</v>
       </c>
-      <c r="F167" s="9">
+      <c r="F167" s="7">
         <v>0.53</v>
       </c>
-      <c r="G167" s="9">
+      <c r="G167" s="7">
         <v>8.06</v>
       </c>
-      <c r="H167" s="12" t="s">
+      <c r="H167" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8572,23 +8634,23 @@
       <c r="A168">
         <v>167</v>
       </c>
-      <c r="B168" s="8"/>
-      <c r="C168" s="9" t="s">
+      <c r="B168" s="15"/>
+      <c r="C168" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D168" s="10">
+      <c r="D168" s="8">
         <v>46303</v>
       </c>
-      <c r="E168" s="9">
+      <c r="E168" s="7">
         <v>0.435</v>
       </c>
-      <c r="F168" s="9">
+      <c r="F168" s="7">
         <v>0.5</v>
       </c>
-      <c r="G168" s="9">
+      <c r="G168" s="7">
         <v>8.4700000000000006</v>
       </c>
-      <c r="H168" s="12" t="s">
+      <c r="H168" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8596,23 +8658,23 @@
       <c r="A169">
         <v>168</v>
       </c>
-      <c r="B169" s="8"/>
-      <c r="C169" s="9" t="s">
+      <c r="B169" s="15"/>
+      <c r="C169" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D169" s="10">
+      <c r="D169" s="8">
         <v>46303</v>
       </c>
-      <c r="E169" s="9">
+      <c r="E169" s="7">
         <v>0.441</v>
       </c>
-      <c r="F169" s="9">
+      <c r="F169" s="7">
         <v>0.48</v>
       </c>
-      <c r="G169" s="9">
+      <c r="G169" s="7">
         <v>8.4</v>
       </c>
-      <c r="H169" s="12" t="s">
+      <c r="H169" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8620,25 +8682,25 @@
       <c r="A170">
         <v>169</v>
       </c>
-      <c r="B170" s="5">
+      <c r="B170" s="14">
         <v>15</v>
       </c>
-      <c r="C170" s="6" t="s">
+      <c r="C170" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D170" s="7">
+      <c r="D170" s="6">
         <v>46303</v>
       </c>
-      <c r="E170" s="6">
+      <c r="E170" s="5">
         <v>0.39300000000000002</v>
       </c>
-      <c r="F170" s="6">
+      <c r="F170" s="5">
         <v>0.3</v>
       </c>
-      <c r="G170" s="6">
+      <c r="G170" s="5">
         <v>8.4499999999999993</v>
       </c>
-      <c r="H170" s="11" t="s">
+      <c r="H170" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8646,23 +8708,23 @@
       <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" s="5"/>
-      <c r="C171" s="6" t="s">
+      <c r="B171" s="14"/>
+      <c r="C171" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D171" s="7">
+      <c r="D171" s="6">
         <v>46303</v>
       </c>
-      <c r="E171" s="6">
+      <c r="E171" s="5">
         <v>0.40100000000000002</v>
       </c>
-      <c r="F171" s="6">
+      <c r="F171" s="5">
         <v>0.3</v>
       </c>
-      <c r="G171" s="6">
+      <c r="G171" s="5">
         <v>8.41</v>
       </c>
-      <c r="H171" s="11" t="s">
+      <c r="H171" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8670,23 +8732,23 @@
       <c r="A172">
         <v>171</v>
       </c>
-      <c r="B172" s="5"/>
-      <c r="C172" s="6" t="s">
+      <c r="B172" s="14"/>
+      <c r="C172" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D172" s="7">
+      <c r="D172" s="6">
         <v>46303</v>
       </c>
-      <c r="E172" s="6">
+      <c r="E172" s="5">
         <v>0.39800000000000002</v>
       </c>
-      <c r="F172" s="6">
+      <c r="F172" s="5">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G172" s="6">
+      <c r="G172" s="5">
         <v>8.43</v>
       </c>
-      <c r="H172" s="11" t="s">
+      <c r="H172" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8694,23 +8756,23 @@
       <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="6" t="s">
+      <c r="B173" s="14"/>
+      <c r="C173" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D173" s="7">
+      <c r="D173" s="6">
         <v>46304</v>
       </c>
-      <c r="E173" s="6">
+      <c r="E173" s="5">
         <v>0.36899999999999999</v>
       </c>
-      <c r="F173" s="6">
+      <c r="F173" s="5">
         <v>0.47</v>
       </c>
-      <c r="G173" s="6">
+      <c r="G173" s="5">
         <v>9.7200000000000006</v>
       </c>
-      <c r="H173" s="11" t="s">
+      <c r="H173" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8718,23 +8780,23 @@
       <c r="A174">
         <v>173</v>
       </c>
-      <c r="B174" s="5"/>
-      <c r="C174" s="6" t="s">
+      <c r="B174" s="14"/>
+      <c r="C174" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D174" s="7">
+      <c r="D174" s="6">
         <v>46304</v>
       </c>
-      <c r="E174" s="6">
+      <c r="E174" s="5">
         <v>0.377</v>
       </c>
-      <c r="F174" s="6">
+      <c r="F174" s="5">
         <v>0.49</v>
       </c>
-      <c r="G174" s="6">
+      <c r="G174" s="5">
         <v>9.34</v>
       </c>
-      <c r="H174" s="11" t="s">
+      <c r="H174" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8742,17 +8804,17 @@
       <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" s="5"/>
-      <c r="C175" s="6" t="s">
+      <c r="B175" s="14"/>
+      <c r="C175" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D175" s="7">
+      <c r="D175" s="6">
         <v>46304</v>
       </c>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="11" t="s">
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8760,17 +8822,17 @@
       <c r="A176">
         <v>175</v>
       </c>
-      <c r="B176" s="5"/>
-      <c r="C176" s="6" t="s">
+      <c r="B176" s="14"/>
+      <c r="C176" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D176" s="7">
+      <c r="D176" s="6">
         <v>46304</v>
       </c>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="11" t="s">
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8778,17 +8840,17 @@
       <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" s="5"/>
-      <c r="C177" s="6" t="s">
+      <c r="B177" s="14"/>
+      <c r="C177" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D177" s="7">
+      <c r="D177" s="6">
         <v>46304</v>
       </c>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="11" t="s">
+      <c r="E177" s="5"/>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
+      <c r="H177" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8796,17 +8858,17 @@
       <c r="A178">
         <v>177</v>
       </c>
-      <c r="B178" s="5"/>
-      <c r="C178" s="6" t="s">
+      <c r="B178" s="14"/>
+      <c r="C178" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D178" s="7">
+      <c r="D178" s="6">
         <v>46304</v>
       </c>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="11" t="s">
+      <c r="E178" s="5"/>
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="H178" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8814,25 +8876,25 @@
       <c r="A179">
         <v>178</v>
       </c>
-      <c r="B179" s="8">
+      <c r="B179" s="15">
         <v>16</v>
       </c>
-      <c r="C179" s="9" t="s">
+      <c r="C179" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D179" s="10">
+      <c r="D179" s="8">
         <v>46305</v>
       </c>
-      <c r="E179" s="9">
+      <c r="E179" s="7">
         <v>0.52300000000000002</v>
       </c>
-      <c r="F179" s="9">
+      <c r="F179" s="7">
         <v>0.41</v>
       </c>
-      <c r="G179" s="9">
+      <c r="G179" s="7">
         <v>11.63</v>
       </c>
-      <c r="H179" s="12" t="s">
+      <c r="H179" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8840,23 +8902,23 @@
       <c r="A180">
         <v>179</v>
       </c>
-      <c r="B180" s="8"/>
-      <c r="C180" s="9" t="s">
+      <c r="B180" s="15"/>
+      <c r="C180" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D180" s="10">
+      <c r="D180" s="8">
         <v>46305</v>
       </c>
-      <c r="E180" s="9">
+      <c r="E180" s="7">
         <v>0.52</v>
       </c>
-      <c r="F180" s="9">
+      <c r="F180" s="7">
         <v>0.45</v>
       </c>
-      <c r="G180" s="9">
+      <c r="G180" s="7">
         <v>11.55</v>
       </c>
-      <c r="H180" s="12" t="s">
+      <c r="H180" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8864,23 +8926,23 @@
       <c r="A181">
         <v>180</v>
       </c>
-      <c r="B181" s="8"/>
-      <c r="C181" s="9" t="s">
+      <c r="B181" s="15"/>
+      <c r="C181" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D181" s="10">
+      <c r="D181" s="8">
         <v>46305</v>
       </c>
-      <c r="E181" s="9">
+      <c r="E181" s="7">
         <v>0.53400000000000003</v>
       </c>
-      <c r="F181" s="9">
+      <c r="F181" s="7">
         <v>0.4</v>
       </c>
-      <c r="G181" s="9">
+      <c r="G181" s="7">
         <v>11.65</v>
       </c>
-      <c r="H181" s="12" t="s">
+      <c r="H181" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8888,23 +8950,23 @@
       <c r="A182">
         <v>181</v>
       </c>
-      <c r="B182" s="8"/>
-      <c r="C182" s="9" t="s">
+      <c r="B182" s="15"/>
+      <c r="C182" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D182" s="10">
+      <c r="D182" s="8">
         <v>46306</v>
       </c>
-      <c r="E182" s="9">
+      <c r="E182" s="7">
         <v>0.42</v>
       </c>
-      <c r="F182" s="9">
+      <c r="F182" s="7">
         <v>0.47</v>
       </c>
-      <c r="G182" s="9">
+      <c r="G182" s="7">
         <v>14.04</v>
       </c>
-      <c r="H182" s="12" t="s">
+      <c r="H182" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8912,23 +8974,23 @@
       <c r="A183">
         <v>182</v>
       </c>
-      <c r="B183" s="8"/>
-      <c r="C183" s="9" t="s">
+      <c r="B183" s="15"/>
+      <c r="C183" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D183" s="10">
+      <c r="D183" s="8">
         <v>46306</v>
       </c>
-      <c r="E183" s="9">
+      <c r="E183" s="7">
         <v>0.41</v>
       </c>
-      <c r="F183" s="9">
+      <c r="F183" s="7">
         <v>0.5</v>
       </c>
-      <c r="G183" s="9">
+      <c r="G183" s="7">
         <v>14.34</v>
       </c>
-      <c r="H183" s="12" t="s">
+      <c r="H183" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8936,23 +8998,23 @@
       <c r="A184">
         <v>183</v>
       </c>
-      <c r="B184" s="8"/>
-      <c r="C184" s="9" t="s">
+      <c r="B184" s="15"/>
+      <c r="C184" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D184" s="10">
+      <c r="D184" s="8">
         <v>46306</v>
       </c>
-      <c r="E184" s="9">
+      <c r="E184" s="7">
         <v>0.4</v>
       </c>
-      <c r="F184" s="9">
+      <c r="F184" s="7">
         <v>0.48</v>
       </c>
-      <c r="G184" s="9">
+      <c r="G184" s="7">
         <v>14.46</v>
       </c>
-      <c r="H184" s="12" t="s">
+      <c r="H184" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8960,23 +9022,23 @@
       <c r="A185">
         <v>184</v>
       </c>
-      <c r="B185" s="8"/>
-      <c r="C185" s="9" t="s">
+      <c r="B185" s="15"/>
+      <c r="C185" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D185" s="10">
+      <c r="D185" s="8">
         <v>46306</v>
       </c>
-      <c r="E185" s="9">
+      <c r="E185" s="7">
         <v>0.66200000000000003</v>
       </c>
-      <c r="F185" s="9">
+      <c r="F185" s="7">
         <v>0.65</v>
       </c>
-      <c r="G185" s="9">
+      <c r="G185" s="7">
         <v>13.21</v>
       </c>
-      <c r="H185" s="12" t="s">
+      <c r="H185" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8984,23 +9046,23 @@
       <c r="A186">
         <v>185</v>
       </c>
-      <c r="B186" s="8"/>
-      <c r="C186" s="9" t="s">
+      <c r="B186" s="15"/>
+      <c r="C186" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D186" s="10">
+      <c r="D186" s="8">
         <v>46306</v>
       </c>
-      <c r="E186" s="9">
+      <c r="E186" s="7">
         <v>0.65700000000000003</v>
       </c>
-      <c r="F186" s="9">
+      <c r="F186" s="7">
         <v>0.66</v>
       </c>
-      <c r="G186" s="9">
+      <c r="G186" s="7">
         <v>12.9</v>
       </c>
-      <c r="H186" s="12" t="s">
+      <c r="H186" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9008,23 +9070,23 @@
       <c r="A187">
         <v>186</v>
       </c>
-      <c r="B187" s="8"/>
-      <c r="C187" s="9" t="s">
+      <c r="B187" s="15"/>
+      <c r="C187" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D187" s="10">
+      <c r="D187" s="8">
         <v>46306</v>
       </c>
-      <c r="E187" s="9">
+      <c r="E187" s="7">
         <v>0.64800000000000002</v>
       </c>
-      <c r="F187" s="9">
+      <c r="F187" s="7">
         <v>0.62</v>
       </c>
-      <c r="G187" s="9">
+      <c r="G187" s="7">
         <v>13.7</v>
       </c>
-      <c r="H187" s="12" t="s">
+      <c r="H187" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9032,23 +9094,23 @@
       <c r="A188">
         <v>187</v>
       </c>
-      <c r="B188" s="8"/>
-      <c r="C188" s="9" t="s">
+      <c r="B188" s="15"/>
+      <c r="C188" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D188" s="10">
+      <c r="D188" s="8">
         <v>46307</v>
       </c>
-      <c r="E188" s="9">
+      <c r="E188" s="7">
         <v>0.38500000000000001</v>
       </c>
-      <c r="F188" s="9">
+      <c r="F188" s="7">
         <v>0.38</v>
       </c>
-      <c r="G188" s="9">
+      <c r="G188" s="7">
         <v>12.24</v>
       </c>
-      <c r="H188" s="12" t="s">
+      <c r="H188" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9056,23 +9118,23 @@
       <c r="A189">
         <v>188</v>
       </c>
-      <c r="B189" s="8"/>
-      <c r="C189" s="9" t="s">
+      <c r="B189" s="15"/>
+      <c r="C189" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D189" s="10">
+      <c r="D189" s="8">
         <v>46307</v>
       </c>
-      <c r="E189" s="9">
+      <c r="E189" s="7">
         <v>0.315</v>
       </c>
-      <c r="F189" s="9">
+      <c r="F189" s="7">
         <v>0.32</v>
       </c>
-      <c r="G189" s="9">
+      <c r="G189" s="7">
         <v>12.18</v>
       </c>
-      <c r="H189" s="12" t="s">
+      <c r="H189" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9080,23 +9142,23 @@
       <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" s="8"/>
-      <c r="C190" s="9" t="s">
+      <c r="B190" s="15"/>
+      <c r="C190" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D190" s="10">
+      <c r="D190" s="8">
         <v>46307</v>
       </c>
-      <c r="E190" s="9">
+      <c r="E190" s="7">
         <v>0.379</v>
       </c>
-      <c r="F190" s="9">
+      <c r="F190" s="7">
         <v>0.38</v>
       </c>
-      <c r="G190" s="9">
+      <c r="G190" s="7">
         <v>13.75</v>
       </c>
-      <c r="H190" s="12" t="s">
+      <c r="H190" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9104,25 +9166,25 @@
       <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" s="5">
+      <c r="B191" s="14">
         <v>17</v>
       </c>
-      <c r="C191" s="6" t="s">
+      <c r="C191" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D191" s="7">
+      <c r="D191" s="6">
         <v>46307</v>
       </c>
-      <c r="E191" s="6">
+      <c r="E191" s="5">
         <v>0.38500000000000001</v>
       </c>
-      <c r="F191" s="6">
+      <c r="F191" s="5">
         <v>0.38</v>
       </c>
-      <c r="G191" s="6">
+      <c r="G191" s="5">
         <v>12.24</v>
       </c>
-      <c r="H191" s="11" t="s">
+      <c r="H191" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9130,23 +9192,23 @@
       <c r="A192">
         <v>191</v>
       </c>
-      <c r="B192" s="5"/>
-      <c r="C192" s="6" t="s">
+      <c r="B192" s="14"/>
+      <c r="C192" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D192" s="7">
+      <c r="D192" s="6">
         <v>46307</v>
       </c>
-      <c r="E192" s="6">
+      <c r="E192" s="5">
         <v>0.315</v>
       </c>
-      <c r="F192" s="6">
+      <c r="F192" s="5">
         <v>0.32</v>
       </c>
-      <c r="G192" s="6">
+      <c r="G192" s="5">
         <v>12.18</v>
       </c>
-      <c r="H192" s="11" t="s">
+      <c r="H192" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9154,23 +9216,23 @@
       <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" s="5"/>
-      <c r="C193" s="6" t="s">
+      <c r="B193" s="14"/>
+      <c r="C193" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D193" s="7">
+      <c r="D193" s="6">
         <v>46307</v>
       </c>
-      <c r="E193" s="6">
+      <c r="E193" s="5">
         <v>0.379</v>
       </c>
-      <c r="F193" s="6">
+      <c r="F193" s="5">
         <v>0.38</v>
       </c>
-      <c r="G193" s="6">
+      <c r="G193" s="5">
         <v>13.75</v>
       </c>
-      <c r="H193" s="11" t="s">
+      <c r="H193" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9178,23 +9240,23 @@
       <c r="A194">
         <v>193</v>
       </c>
-      <c r="B194" s="5"/>
-      <c r="C194" s="6" t="s">
+      <c r="B194" s="14"/>
+      <c r="C194" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D194" s="7">
+      <c r="D194" s="6">
         <v>46307</v>
       </c>
-      <c r="E194" s="6">
+      <c r="E194" s="5">
         <v>0.33</v>
       </c>
-      <c r="F194" s="6">
+      <c r="F194" s="5">
         <v>0.46</v>
       </c>
-      <c r="G194" s="6">
+      <c r="G194" s="5">
         <v>11.45</v>
       </c>
-      <c r="H194" s="11" t="s">
+      <c r="H194" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9202,23 +9264,23 @@
       <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" s="5"/>
-      <c r="C195" s="6" t="s">
+      <c r="B195" s="14"/>
+      <c r="C195" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D195" s="7">
+      <c r="D195" s="6">
         <v>46307</v>
       </c>
-      <c r="E195" s="6">
+      <c r="E195" s="5">
         <v>0.33700000000000002</v>
       </c>
-      <c r="F195" s="6">
+      <c r="F195" s="5">
         <v>0.42</v>
       </c>
-      <c r="G195" s="6">
+      <c r="G195" s="5">
         <v>11.8</v>
       </c>
-      <c r="H195" s="11" t="s">
+      <c r="H195" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9226,23 +9288,23 @@
       <c r="A196">
         <v>195</v>
       </c>
-      <c r="B196" s="5"/>
-      <c r="C196" s="6" t="s">
+      <c r="B196" s="14"/>
+      <c r="C196" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D196" s="7">
+      <c r="D196" s="6">
         <v>46307</v>
       </c>
-      <c r="E196" s="6">
+      <c r="E196" s="5">
         <v>0.36099999999999999</v>
       </c>
-      <c r="F196" s="6">
+      <c r="F196" s="5">
         <v>0.41</v>
       </c>
-      <c r="G196" s="6">
+      <c r="G196" s="5">
         <v>11.57</v>
       </c>
-      <c r="H196" s="11" t="s">
+      <c r="H196" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9250,23 +9312,23 @@
       <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" s="5"/>
-      <c r="C197" s="6" t="s">
+      <c r="B197" s="14"/>
+      <c r="C197" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D197" s="7">
+      <c r="D197" s="6">
         <v>46308</v>
       </c>
-      <c r="E197" s="6">
+      <c r="E197" s="5">
         <v>0.32400000000000001</v>
       </c>
-      <c r="F197" s="6">
+      <c r="F197" s="5">
         <v>0.39</v>
       </c>
-      <c r="G197" s="6">
+      <c r="G197" s="5">
         <v>9.92</v>
       </c>
-      <c r="H197" s="11" t="s">
+      <c r="H197" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9274,23 +9336,23 @@
       <c r="A198">
         <v>197</v>
       </c>
-      <c r="B198" s="5"/>
-      <c r="C198" s="6" t="s">
+      <c r="B198" s="14"/>
+      <c r="C198" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D198" s="7">
+      <c r="D198" s="6">
         <v>46308</v>
       </c>
-      <c r="E198" s="6">
+      <c r="E198" s="5">
         <v>0.375</v>
       </c>
-      <c r="F198" s="6">
+      <c r="F198" s="5">
         <v>0.47</v>
       </c>
-      <c r="G198" s="6">
+      <c r="G198" s="5">
         <v>10.71</v>
       </c>
-      <c r="H198" s="11" t="s">
+      <c r="H198" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9298,23 +9360,23 @@
       <c r="A199">
         <v>198</v>
       </c>
-      <c r="B199" s="5"/>
-      <c r="C199" s="6" t="s">
+      <c r="B199" s="14"/>
+      <c r="C199" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D199" s="7">
+      <c r="D199" s="6">
         <v>46308</v>
       </c>
-      <c r="E199" s="6">
+      <c r="E199" s="5">
         <v>0.35</v>
       </c>
-      <c r="F199" s="6">
+      <c r="F199" s="5">
         <v>0.35</v>
       </c>
-      <c r="G199" s="6">
+      <c r="G199" s="5">
         <v>10.58</v>
       </c>
-      <c r="H199" s="11" t="s">
+      <c r="H199" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9322,25 +9384,25 @@
       <c r="A200">
         <v>199</v>
       </c>
-      <c r="B200" s="8">
+      <c r="B200" s="15">
         <v>18</v>
       </c>
-      <c r="C200" s="9" t="s">
+      <c r="C200" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D200" s="10">
+      <c r="D200" s="8">
         <v>46308</v>
       </c>
-      <c r="E200" s="9">
+      <c r="E200" s="7">
         <v>0.41599999999999998</v>
       </c>
-      <c r="F200" s="9">
+      <c r="F200" s="7">
         <v>0.4</v>
       </c>
-      <c r="G200" s="9">
+      <c r="G200" s="7">
         <v>8.52</v>
       </c>
-      <c r="H200" s="12" t="s">
+      <c r="H200" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9348,23 +9410,23 @@
       <c r="A201">
         <v>200</v>
       </c>
-      <c r="B201" s="8"/>
-      <c r="C201" s="9" t="s">
+      <c r="B201" s="15"/>
+      <c r="C201" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D201" s="10">
+      <c r="D201" s="8">
         <v>46308</v>
       </c>
-      <c r="E201" s="9">
+      <c r="E201" s="7">
         <v>0.377</v>
       </c>
-      <c r="F201" s="9">
+      <c r="F201" s="7">
         <v>0.34</v>
       </c>
-      <c r="G201" s="9">
+      <c r="G201" s="7">
         <v>8.65</v>
       </c>
-      <c r="H201" s="12" t="s">
+      <c r="H201" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9372,23 +9434,23 @@
       <c r="A202">
         <v>201</v>
       </c>
-      <c r="B202" s="8"/>
-      <c r="C202" s="9" t="s">
+      <c r="B202" s="15"/>
+      <c r="C202" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D202" s="10">
+      <c r="D202" s="8">
         <v>46308</v>
       </c>
-      <c r="E202" s="9">
+      <c r="E202" s="7">
         <v>0.40400000000000003</v>
       </c>
-      <c r="F202" s="9">
+      <c r="F202" s="7">
         <v>0.43</v>
       </c>
-      <c r="G202" s="9">
+      <c r="G202" s="7">
         <v>8.48</v>
       </c>
-      <c r="H202" s="12" t="s">
+      <c r="H202" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9396,23 +9458,23 @@
       <c r="A203">
         <v>202</v>
       </c>
-      <c r="B203" s="8"/>
-      <c r="C203" s="9" t="s">
+      <c r="B203" s="15"/>
+      <c r="C203" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="10">
+      <c r="D203" s="8">
         <v>46309</v>
       </c>
-      <c r="E203" s="9">
+      <c r="E203" s="7">
         <v>0.317</v>
       </c>
-      <c r="F203" s="9">
+      <c r="F203" s="7">
         <v>0.33</v>
       </c>
-      <c r="G203" s="9">
+      <c r="G203" s="7">
         <v>8.6199999999999992</v>
       </c>
-      <c r="H203" s="12" t="s">
+      <c r="H203" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9420,23 +9482,23 @@
       <c r="A204">
         <v>203</v>
       </c>
-      <c r="B204" s="8"/>
-      <c r="C204" s="9" t="s">
+      <c r="B204" s="15"/>
+      <c r="C204" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D204" s="10">
+      <c r="D204" s="8">
         <v>46309</v>
       </c>
-      <c r="E204" s="9">
+      <c r="E204" s="7">
         <v>0.38300000000000001</v>
       </c>
-      <c r="F204" s="9">
+      <c r="F204" s="7">
         <v>0.33</v>
       </c>
-      <c r="G204" s="9">
+      <c r="G204" s="7">
         <v>7.71</v>
       </c>
-      <c r="H204" s="12" t="s">
+      <c r="H204" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9444,23 +9506,23 @@
       <c r="A205">
         <v>204</v>
       </c>
-      <c r="B205" s="8"/>
-      <c r="C205" s="9" t="s">
+      <c r="B205" s="15"/>
+      <c r="C205" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D205" s="10">
+      <c r="D205" s="8">
         <v>46309</v>
       </c>
-      <c r="E205" s="9">
+      <c r="E205" s="7">
         <v>0.35199999999999998</v>
       </c>
-      <c r="F205" s="9">
+      <c r="F205" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G205" s="9">
+      <c r="G205" s="7">
         <v>6.38</v>
       </c>
-      <c r="H205" s="12" t="s">
+      <c r="H205" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9468,23 +9530,23 @@
       <c r="A206">
         <v>205</v>
       </c>
-      <c r="B206" s="8"/>
-      <c r="C206" s="9" t="s">
+      <c r="B206" s="15"/>
+      <c r="C206" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D206" s="10">
+      <c r="D206" s="8">
         <v>46309</v>
       </c>
-      <c r="E206" s="9">
+      <c r="E206" s="7">
         <v>0.435</v>
       </c>
-      <c r="F206" s="9">
+      <c r="F206" s="7">
         <v>0.2</v>
       </c>
-      <c r="G206" s="9">
+      <c r="G206" s="7">
         <v>6.22</v>
       </c>
-      <c r="H206" s="12" t="s">
+      <c r="H206" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9492,23 +9554,23 @@
       <c r="A207">
         <v>206</v>
       </c>
-      <c r="B207" s="8"/>
-      <c r="C207" s="9" t="s">
+      <c r="B207" s="15"/>
+      <c r="C207" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D207" s="10">
+      <c r="D207" s="8">
         <v>46309</v>
       </c>
-      <c r="E207" s="9">
+      <c r="E207" s="7">
         <v>0.42199999999999999</v>
       </c>
-      <c r="F207" s="9">
+      <c r="F207" s="7">
         <v>0.22</v>
       </c>
-      <c r="G207" s="9">
+      <c r="G207" s="7">
         <v>8.52</v>
       </c>
-      <c r="H207" s="12" t="s">
+      <c r="H207" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9516,23 +9578,23 @@
       <c r="A208">
         <v>207</v>
       </c>
-      <c r="B208" s="8"/>
-      <c r="C208" s="9" t="s">
+      <c r="B208" s="15"/>
+      <c r="C208" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D208" s="10">
+      <c r="D208" s="8">
         <v>46309</v>
       </c>
-      <c r="E208" s="9">
+      <c r="E208" s="7">
         <v>0.44900000000000001</v>
       </c>
-      <c r="F208" s="9">
+      <c r="F208" s="7">
         <v>0.21</v>
       </c>
-      <c r="G208" s="9">
+      <c r="G208" s="7">
         <v>6.4</v>
       </c>
-      <c r="H208" s="12" t="s">
+      <c r="H208" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9540,19 +9602,19 @@
       <c r="A209">
         <v>208</v>
       </c>
-      <c r="B209" s="5">
+      <c r="B209" s="14">
         <v>19</v>
       </c>
-      <c r="C209" s="6" t="s">
+      <c r="C209" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D209" s="7">
+      <c r="D209" s="6">
         <v>46310</v>
       </c>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="11" t="s">
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+      <c r="H209" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9560,17 +9622,17 @@
       <c r="A210">
         <v>209</v>
       </c>
-      <c r="B210" s="5"/>
-      <c r="C210" s="6" t="s">
+      <c r="B210" s="14"/>
+      <c r="C210" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D210" s="7">
+      <c r="D210" s="6">
         <v>46310</v>
       </c>
-      <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
-      <c r="G210" s="6"/>
-      <c r="H210" s="11" t="s">
+      <c r="E210" s="5"/>
+      <c r="F210" s="5"/>
+      <c r="G210" s="5"/>
+      <c r="H210" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9578,17 +9640,17 @@
       <c r="A211">
         <v>210</v>
       </c>
-      <c r="B211" s="5"/>
-      <c r="C211" s="6" t="s">
+      <c r="B211" s="14"/>
+      <c r="C211" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D211" s="7">
+      <c r="D211" s="6">
         <v>46310</v>
       </c>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
-      <c r="H211" s="11" t="s">
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="5"/>
+      <c r="H211" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9596,23 +9658,23 @@
       <c r="A212">
         <v>211</v>
       </c>
-      <c r="B212" s="5"/>
-      <c r="C212" s="6" t="s">
+      <c r="B212" s="14"/>
+      <c r="C212" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D212" s="7">
+      <c r="D212" s="6">
         <v>46310</v>
       </c>
-      <c r="E212" s="6">
+      <c r="E212" s="5">
         <v>0.3</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F212" s="5">
         <v>0.52</v>
       </c>
-      <c r="G212" s="6">
+      <c r="G212" s="5">
         <v>14.552</v>
       </c>
-      <c r="H212" s="11" t="s">
+      <c r="H212" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9620,23 +9682,23 @@
       <c r="A213">
         <v>212</v>
       </c>
-      <c r="B213" s="5"/>
-      <c r="C213" s="6" t="s">
+      <c r="B213" s="14"/>
+      <c r="C213" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D213" s="7">
+      <c r="D213" s="6">
         <v>46310</v>
       </c>
-      <c r="E213" s="6">
+      <c r="E213" s="5">
         <v>0.29099999999999998</v>
       </c>
-      <c r="F213" s="6">
+      <c r="F213" s="5">
         <v>0.41</v>
       </c>
-      <c r="G213" s="6">
+      <c r="G213" s="5">
         <v>11.872999999999999</v>
       </c>
-      <c r="H213" s="11" t="s">
+      <c r="H213" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9644,23 +9706,23 @@
       <c r="A214">
         <v>213</v>
       </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="6" t="s">
+      <c r="B214" s="14"/>
+      <c r="C214" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D214" s="7">
+      <c r="D214" s="6">
         <v>46310</v>
       </c>
-      <c r="E214" s="6">
+      <c r="E214" s="5">
         <v>0.27100000000000002</v>
       </c>
-      <c r="F214" s="6">
+      <c r="F214" s="5">
         <v>0.41</v>
       </c>
-      <c r="G214" s="6">
+      <c r="G214" s="5">
         <v>12.935</v>
       </c>
-      <c r="H214" s="11" t="s">
+      <c r="H214" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9668,23 +9730,23 @@
       <c r="A215">
         <v>214</v>
       </c>
-      <c r="B215" s="5"/>
-      <c r="C215" s="6" t="s">
+      <c r="B215" s="14"/>
+      <c r="C215" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D215" s="7">
+      <c r="D215" s="6">
         <v>46310</v>
       </c>
-      <c r="E215" s="6">
+      <c r="E215" s="5">
         <v>0.29299999999999998</v>
       </c>
-      <c r="F215" s="6">
+      <c r="F215" s="5">
         <v>0.16</v>
       </c>
-      <c r="G215" s="6">
+      <c r="G215" s="5">
         <v>12.879</v>
       </c>
-      <c r="H215" s="11" t="s">
+      <c r="H215" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9692,23 +9754,23 @@
       <c r="A216">
         <v>215</v>
       </c>
-      <c r="B216" s="5"/>
-      <c r="C216" s="6" t="s">
+      <c r="B216" s="14"/>
+      <c r="C216" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D216" s="7">
+      <c r="D216" s="6">
         <v>46310</v>
       </c>
-      <c r="E216" s="6">
+      <c r="E216" s="5">
         <v>0.32500000000000001</v>
       </c>
-      <c r="F216" s="6">
+      <c r="F216" s="5">
         <v>0.26</v>
       </c>
-      <c r="G216" s="6">
+      <c r="G216" s="5">
         <v>14.369</v>
       </c>
-      <c r="H216" s="11" t="s">
+      <c r="H216" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9716,23 +9778,23 @@
       <c r="A217">
         <v>216</v>
       </c>
-      <c r="B217" s="5"/>
-      <c r="C217" s="6" t="s">
+      <c r="B217" s="14"/>
+      <c r="C217" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D217" s="7">
+      <c r="D217" s="6">
         <v>46310</v>
       </c>
-      <c r="E217" s="6">
+      <c r="E217" s="5">
         <v>0.36099999999999999</v>
       </c>
-      <c r="F217" s="6">
+      <c r="F217" s="5">
         <v>0.24</v>
       </c>
-      <c r="G217" s="6">
+      <c r="G217" s="5">
         <v>14.054</v>
       </c>
-      <c r="H217" s="11" t="s">
+      <c r="H217" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9740,23 +9802,23 @@
       <c r="A218">
         <v>217</v>
       </c>
-      <c r="B218" s="5"/>
-      <c r="C218" s="6" t="s">
+      <c r="B218" s="14"/>
+      <c r="C218" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D218" s="7">
+      <c r="D218" s="6">
         <v>46310</v>
       </c>
-      <c r="E218" s="6">
+      <c r="E218" s="5">
         <v>0.307</v>
       </c>
-      <c r="F218" s="6">
+      <c r="F218" s="5">
         <v>0.18</v>
       </c>
-      <c r="G218" s="6">
+      <c r="G218" s="5">
         <v>14.391999999999999</v>
       </c>
-      <c r="H218" s="11" t="s">
+      <c r="H218" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9764,23 +9826,23 @@
       <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" s="5"/>
-      <c r="C219" s="6" t="s">
+      <c r="B219" s="14"/>
+      <c r="C219" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D219" s="7">
+      <c r="D219" s="6">
         <v>46310</v>
       </c>
-      <c r="E219" s="6">
+      <c r="E219" s="5">
         <v>0.24</v>
       </c>
-      <c r="F219" s="6">
+      <c r="F219" s="5">
         <v>0.3</v>
       </c>
-      <c r="G219" s="6">
+      <c r="G219" s="5">
         <v>13.632999999999999</v>
       </c>
-      <c r="H219" s="11" t="s">
+      <c r="H219" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9788,23 +9850,23 @@
       <c r="A220">
         <v>219</v>
       </c>
-      <c r="B220" s="5"/>
-      <c r="C220" s="6" t="s">
+      <c r="B220" s="14"/>
+      <c r="C220" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D220" s="7">
+      <c r="D220" s="6">
         <v>46310</v>
       </c>
-      <c r="E220" s="6">
+      <c r="E220" s="5">
         <v>0.224</v>
       </c>
-      <c r="F220" s="6">
+      <c r="F220" s="5">
         <v>0.31</v>
       </c>
-      <c r="G220" s="6">
+      <c r="G220" s="5">
         <v>12.032999999999999</v>
       </c>
-      <c r="H220" s="11" t="s">
+      <c r="H220" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9812,23 +9874,23 @@
       <c r="A221">
         <v>220</v>
       </c>
-      <c r="B221" s="5"/>
-      <c r="C221" s="6" t="s">
+      <c r="B221" s="14"/>
+      <c r="C221" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D221" s="7">
+      <c r="D221" s="6">
         <v>46310</v>
       </c>
-      <c r="E221" s="6">
+      <c r="E221" s="5">
         <v>0.219</v>
       </c>
-      <c r="F221" s="6">
+      <c r="F221" s="5">
         <v>0.26</v>
       </c>
-      <c r="G221" s="6">
+      <c r="G221" s="5">
         <v>12.250999999999999</v>
       </c>
-      <c r="H221" s="11" t="s">
+      <c r="H221" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9836,23 +9898,23 @@
       <c r="A222">
         <v>221</v>
       </c>
-      <c r="B222" s="5"/>
-      <c r="C222" s="6" t="s">
+      <c r="B222" s="14"/>
+      <c r="C222" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D222" s="7">
+      <c r="D222" s="6">
         <v>46311</v>
       </c>
-      <c r="E222" s="6">
+      <c r="E222" s="5">
         <v>0.37</v>
       </c>
-      <c r="F222" s="6">
+      <c r="F222" s="5">
         <v>0.61</v>
       </c>
-      <c r="G222" s="6">
+      <c r="G222" s="5">
         <v>12.27</v>
       </c>
-      <c r="H222" s="11" t="s">
+      <c r="H222" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9860,23 +9922,23 @@
       <c r="A223">
         <v>222</v>
       </c>
-      <c r="B223" s="5"/>
-      <c r="C223" s="6" t="s">
+      <c r="B223" s="14"/>
+      <c r="C223" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D223" s="7">
+      <c r="D223" s="6">
         <v>46311</v>
       </c>
-      <c r="E223" s="6">
+      <c r="E223" s="5">
         <v>0.35599999999999998</v>
       </c>
-      <c r="F223" s="6">
+      <c r="F223" s="5">
         <v>0.62</v>
       </c>
-      <c r="G223" s="6">
+      <c r="G223" s="5">
         <v>14.506</v>
       </c>
-      <c r="H223" s="11" t="s">
+      <c r="H223" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9884,23 +9946,23 @@
       <c r="A224">
         <v>223</v>
       </c>
-      <c r="B224" s="5"/>
-      <c r="C224" s="6" t="s">
+      <c r="B224" s="14"/>
+      <c r="C224" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D224" s="7">
+      <c r="D224" s="6">
         <v>46311</v>
       </c>
-      <c r="E224" s="6">
+      <c r="E224" s="5">
         <v>0.378</v>
       </c>
-      <c r="F224" s="6">
+      <c r="F224" s="5">
         <v>0.63</v>
       </c>
-      <c r="G224" s="6">
+      <c r="G224" s="5">
         <v>15.176</v>
       </c>
-      <c r="H224" s="11" t="s">
+      <c r="H224" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9908,23 +9970,23 @@
       <c r="A225">
         <v>224</v>
       </c>
-      <c r="B225" s="5"/>
-      <c r="C225" s="6" t="s">
+      <c r="B225" s="14"/>
+      <c r="C225" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D225" s="7">
+      <c r="D225" s="6">
         <v>46311</v>
       </c>
-      <c r="E225" s="6">
+      <c r="E225" s="5">
         <v>0.38400000000000001</v>
       </c>
-      <c r="F225" s="6">
+      <c r="F225" s="5">
         <v>0.64</v>
       </c>
-      <c r="G225" s="6">
+      <c r="G225" s="5">
         <v>14.336</v>
       </c>
-      <c r="H225" s="11" t="s">
+      <c r="H225" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9932,23 +9994,23 @@
       <c r="A226">
         <v>225</v>
       </c>
-      <c r="B226" s="5"/>
-      <c r="C226" s="6" t="s">
+      <c r="B226" s="14"/>
+      <c r="C226" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D226" s="7">
+      <c r="D226" s="6">
         <v>46311</v>
       </c>
-      <c r="E226" s="6">
+      <c r="E226" s="5">
         <v>0.39900000000000002</v>
       </c>
-      <c r="F226" s="6">
+      <c r="F226" s="5">
         <v>0.66</v>
       </c>
-      <c r="G226" s="6">
+      <c r="G226" s="5">
         <v>14.525</v>
       </c>
-      <c r="H226" s="11" t="s">
+      <c r="H226" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9956,23 +10018,23 @@
       <c r="A227">
         <v>226</v>
       </c>
-      <c r="B227" s="5"/>
-      <c r="C227" s="6" t="s">
+      <c r="B227" s="14"/>
+      <c r="C227" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D227" s="7">
+      <c r="D227" s="6">
         <v>46311</v>
       </c>
-      <c r="E227" s="6">
+      <c r="E227" s="5">
         <v>0.377</v>
       </c>
-      <c r="F227" s="6">
+      <c r="F227" s="5">
         <v>0.65</v>
       </c>
-      <c r="G227" s="6">
+      <c r="G227" s="5">
         <v>12.862</v>
       </c>
-      <c r="H227" s="11" t="s">
+      <c r="H227" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9980,28 +10042,91 @@
       <c r="A228">
         <v>227</v>
       </c>
-      <c r="B228" s="5"/>
-      <c r="C228" s="6" t="s">
+      <c r="B228" s="14"/>
+      <c r="C228" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D228" s="7">
+      <c r="D228" s="6">
         <v>46311</v>
       </c>
-      <c r="E228" s="6">
+      <c r="E228" s="5">
         <v>0.38400000000000001</v>
       </c>
-      <c r="F228" s="6">
+      <c r="F228" s="5">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G228" s="6">
+      <c r="G228" s="5">
         <v>13.039</v>
       </c>
-      <c r="H228" s="11" t="s">
-        <v>29</v>
+      <c r="H228" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="D229" t="s">
+        <v>54</v>
+      </c>
+      <c r="E229">
+        <f>MAX(E2:E228)</f>
+        <v>1.468</v>
+      </c>
+      <c r="F229">
+        <f t="shared" ref="F229:G229" si="0">MAX(F2:F228)</f>
+        <v>10.11</v>
+      </c>
+      <c r="G229">
+        <f t="shared" si="0"/>
+        <v>27.939</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="D230" t="s">
+        <v>55</v>
+      </c>
+      <c r="E230">
+        <f>MIN(E2:E228)</f>
+        <v>0.219</v>
+      </c>
+      <c r="F230">
+        <f t="shared" ref="F230:G230" si="1">MIN(F2:F228)</f>
+        <v>0.01</v>
+      </c>
+      <c r="G230">
+        <f t="shared" si="1"/>
+        <v>5.9560000000000004</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="D231" t="s">
+        <v>56</v>
+      </c>
+      <c r="E231" s="16">
+        <f>AVERAGE(E2:E228)</f>
+        <v>0.58585046728971923</v>
+      </c>
+      <c r="F231" s="16">
+        <f t="shared" ref="F231:G231" si="2">AVERAGE(F2:F228)</f>
+        <v>0.83742056074766358</v>
+      </c>
+      <c r="G231" s="16">
+        <f t="shared" si="2"/>
+        <v>12.438074766355133</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B128:B145"/>
+    <mergeCell ref="B2:B13"/>
+    <mergeCell ref="B14:B22"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="B35:B49"/>
+    <mergeCell ref="B50:B58"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="B65:B73"/>
+    <mergeCell ref="B74:B85"/>
+    <mergeCell ref="B86:B97"/>
+    <mergeCell ref="B98:B118"/>
+    <mergeCell ref="B119:B127"/>
     <mergeCell ref="B209:B228"/>
     <mergeCell ref="B146:B160"/>
     <mergeCell ref="B161:B169"/>
@@ -10009,18 +10134,6 @@
     <mergeCell ref="B179:B190"/>
     <mergeCell ref="B191:B199"/>
     <mergeCell ref="B200:B208"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B74:B85"/>
-    <mergeCell ref="B86:B97"/>
-    <mergeCell ref="B98:B118"/>
-    <mergeCell ref="B119:B127"/>
-    <mergeCell ref="B128:B145"/>
-    <mergeCell ref="B2:B13"/>
-    <mergeCell ref="B14:B22"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="B35:B49"/>
-    <mergeCell ref="B50:B58"/>
-    <mergeCell ref="B59:B64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PRODUKSI/REPORT/LF_Ball_Mill_Metallurgical_Report.xlsx
+++ b/PRODUKSI/REPORT/LF_Ball_Mill_Metallurgical_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C2D6AE-724D-46C9-BF2C-285A81FAAB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496E57BD-7A55-4A4F-B224-1C3F11CAC065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="54">
   <si>
     <t>Periode</t>
   </si>
@@ -221,23 +221,13 @@
   <si>
     <t xml:space="preserve">Leach Feed BALL MILL </t>
   </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -262,7 +252,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,8 +276,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -295,11 +291,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -326,14 +337,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3421,7 +3443,7 @@
       </c>
     </row>
     <row r="21" spans="2:23">
-      <c r="W21" s="17"/>
+      <c r="W21" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3431,7 +3453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -4450,6 +4472,23 @@
       </c>
       <c r="H39">
         <v>11.662100000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="D40">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E40">
+        <v>8.41</v>
       </c>
     </row>
   </sheetData>
@@ -4613,7 +4652,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I236"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -4654,7 +4693,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="16">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -4680,7 +4719,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="5" t="s">
         <v>37</v>
       </c>
@@ -4704,7 +4743,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="5" t="s">
         <v>38</v>
       </c>
@@ -4728,7 +4767,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="14"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
@@ -4752,7 +4791,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="5" t="s">
         <v>40</v>
       </c>
@@ -4776,7 +4815,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="5" t="s">
         <v>41</v>
       </c>
@@ -4800,7 +4839,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="14"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
@@ -4824,7 +4863,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
@@ -4848,7 +4887,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="14"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
@@ -4872,7 +4911,7 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="14"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="5" t="s">
         <v>39</v>
       </c>
@@ -4896,7 +4935,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
@@ -4920,7 +4959,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="14"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="5" t="s">
         <v>41</v>
       </c>
@@ -5162,7 +5201,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="16">
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -5188,7 +5227,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="14"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="5" t="s">
         <v>40</v>
       </c>
@@ -5212,7 +5251,7 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="14"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="5" t="s">
         <v>41</v>
       </c>
@@ -5236,7 +5275,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="14"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="5" t="s">
         <v>36</v>
       </c>
@@ -5260,7 +5299,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="14"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="5" t="s">
         <v>37</v>
       </c>
@@ -5284,7 +5323,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="14"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="5" t="s">
         <v>38</v>
       </c>
@@ -5308,7 +5347,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="14"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="5" t="s">
         <v>39</v>
       </c>
@@ -5332,7 +5371,7 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
@@ -5356,7 +5395,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="14"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="5" t="s">
         <v>41</v>
       </c>
@@ -5380,7 +5419,7 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="14"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="5" t="s">
         <v>36</v>
       </c>
@@ -5404,7 +5443,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="14"/>
+      <c r="B33" s="16"/>
       <c r="C33" s="5" t="s">
         <v>37</v>
       </c>
@@ -5428,7 +5467,7 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="14"/>
+      <c r="B34" s="16"/>
       <c r="C34" s="5" t="s">
         <v>38</v>
       </c>
@@ -5796,7 +5835,7 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="16">
         <v>5</v>
       </c>
       <c r="C50" s="5" t="s">
@@ -5822,7 +5861,7 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="14"/>
+      <c r="B51" s="16"/>
       <c r="C51" s="5" t="s">
         <v>37</v>
       </c>
@@ -5846,7 +5885,7 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="14"/>
+      <c r="B52" s="16"/>
       <c r="C52" s="5" t="s">
         <v>38</v>
       </c>
@@ -5870,7 +5909,7 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="14"/>
+      <c r="B53" s="16"/>
       <c r="C53" s="5" t="s">
         <v>39</v>
       </c>
@@ -5894,7 +5933,7 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="14"/>
+      <c r="B54" s="16"/>
       <c r="C54" s="5" t="s">
         <v>40</v>
       </c>
@@ -5918,7 +5957,7 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="14"/>
+      <c r="B55" s="16"/>
       <c r="C55" s="5" t="s">
         <v>41</v>
       </c>
@@ -5942,7 +5981,7 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="14"/>
+      <c r="B56" s="16"/>
       <c r="C56" s="5" t="s">
         <v>36</v>
       </c>
@@ -5966,7 +6005,7 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="14"/>
+      <c r="B57" s="16"/>
       <c r="C57" s="5" t="s">
         <v>37</v>
       </c>
@@ -5990,7 +6029,7 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="14"/>
+      <c r="B58" s="16"/>
       <c r="C58" s="5" t="s">
         <v>38</v>
       </c>
@@ -6160,7 +6199,7 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="14">
+      <c r="B65" s="16">
         <v>7</v>
       </c>
       <c r="C65" s="5" t="s">
@@ -6186,7 +6225,7 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="14"/>
+      <c r="B66" s="16"/>
       <c r="C66" s="5" t="s">
         <v>40</v>
       </c>
@@ -6210,7 +6249,7 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="14"/>
+      <c r="B67" s="16"/>
       <c r="C67" s="5" t="s">
         <v>41</v>
       </c>
@@ -6234,7 +6273,7 @@
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="14"/>
+      <c r="B68" s="16"/>
       <c r="C68" s="5" t="s">
         <v>36</v>
       </c>
@@ -6258,7 +6297,7 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="14"/>
+      <c r="B69" s="16"/>
       <c r="C69" s="5" t="s">
         <v>37</v>
       </c>
@@ -6282,7 +6321,7 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="14"/>
+      <c r="B70" s="16"/>
       <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
@@ -6306,7 +6345,7 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="14"/>
+      <c r="B71" s="16"/>
       <c r="C71" s="5" t="s">
         <v>39</v>
       </c>
@@ -6330,7 +6369,7 @@
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="14"/>
+      <c r="B72" s="16"/>
       <c r="C72" s="5" t="s">
         <v>40</v>
       </c>
@@ -6354,7 +6393,7 @@
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="14"/>
+      <c r="B73" s="16"/>
       <c r="C73" s="5" t="s">
         <v>41</v>
       </c>
@@ -6668,7 +6707,7 @@
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="14">
+      <c r="B86" s="16">
         <v>9</v>
       </c>
       <c r="C86" s="5" t="s">
@@ -6694,7 +6733,7 @@
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="14"/>
+      <c r="B87" s="16"/>
       <c r="C87" s="5" t="s">
         <v>37</v>
       </c>
@@ -6718,7 +6757,7 @@
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="14"/>
+      <c r="B88" s="16"/>
       <c r="C88" s="5" t="s">
         <v>38</v>
       </c>
@@ -6742,7 +6781,7 @@
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="14"/>
+      <c r="B89" s="16"/>
       <c r="C89" s="5" t="s">
         <v>39</v>
       </c>
@@ -6766,7 +6805,7 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="14"/>
+      <c r="B90" s="16"/>
       <c r="C90" s="5" t="s">
         <v>40</v>
       </c>
@@ -6790,7 +6829,7 @@
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="14"/>
+      <c r="B91" s="16"/>
       <c r="C91" s="5" t="s">
         <v>41</v>
       </c>
@@ -6814,7 +6853,7 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="14"/>
+      <c r="B92" s="16"/>
       <c r="C92" s="5" t="s">
         <v>36</v>
       </c>
@@ -6838,7 +6877,7 @@
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="14"/>
+      <c r="B93" s="16"/>
       <c r="C93" s="5" t="s">
         <v>37</v>
       </c>
@@ -6862,7 +6901,7 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="14"/>
+      <c r="B94" s="16"/>
       <c r="C94" s="5" t="s">
         <v>38</v>
       </c>
@@ -6886,7 +6925,7 @@
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="14"/>
+      <c r="B95" s="16"/>
       <c r="C95" s="5" t="s">
         <v>39</v>
       </c>
@@ -6910,7 +6949,7 @@
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="14"/>
+      <c r="B96" s="16"/>
       <c r="C96" s="5" t="s">
         <v>40</v>
       </c>
@@ -6934,7 +6973,7 @@
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="14"/>
+      <c r="B97" s="16"/>
       <c r="C97" s="5" t="s">
         <v>41</v>
       </c>
@@ -7464,7 +7503,7 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" s="14">
+      <c r="B119" s="16">
         <v>11</v>
       </c>
       <c r="C119" s="5" t="s">
@@ -7490,7 +7529,7 @@
       <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" s="14"/>
+      <c r="B120" s="16"/>
       <c r="C120" s="5" t="s">
         <v>40</v>
       </c>
@@ -7514,7 +7553,7 @@
       <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" s="14"/>
+      <c r="B121" s="16"/>
       <c r="C121" s="5" t="s">
         <v>41</v>
       </c>
@@ -7538,7 +7577,7 @@
       <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" s="14"/>
+      <c r="B122" s="16"/>
       <c r="C122" s="5" t="s">
         <v>36</v>
       </c>
@@ -7562,7 +7601,7 @@
       <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" s="14"/>
+      <c r="B123" s="16"/>
       <c r="C123" s="5" t="s">
         <v>37</v>
       </c>
@@ -7586,7 +7625,7 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" s="14"/>
+      <c r="B124" s="16"/>
       <c r="C124" s="5" t="s">
         <v>38</v>
       </c>
@@ -7610,7 +7649,7 @@
       <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" s="14"/>
+      <c r="B125" s="16"/>
       <c r="C125" s="5" t="s">
         <v>39</v>
       </c>
@@ -7628,7 +7667,7 @@
       <c r="A126">
         <v>125</v>
       </c>
-      <c r="B126" s="14"/>
+      <c r="B126" s="16"/>
       <c r="C126" s="5" t="s">
         <v>40</v>
       </c>
@@ -7646,7 +7685,7 @@
       <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" s="14"/>
+      <c r="B127" s="16"/>
       <c r="C127" s="5" t="s">
         <v>41</v>
       </c>
@@ -8098,7 +8137,7 @@
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" s="14">
+      <c r="B146" s="16">
         <v>13</v>
       </c>
       <c r="C146" s="5" t="s">
@@ -8124,7 +8163,7 @@
       <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" s="14"/>
+      <c r="B147" s="16"/>
       <c r="C147" s="5" t="s">
         <v>40</v>
       </c>
@@ -8148,7 +8187,7 @@
       <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" s="14"/>
+      <c r="B148" s="16"/>
       <c r="C148" s="5" t="s">
         <v>41</v>
       </c>
@@ -8172,7 +8211,7 @@
       <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" s="14"/>
+      <c r="B149" s="16"/>
       <c r="C149" s="5" t="s">
         <v>36</v>
       </c>
@@ -8196,7 +8235,7 @@
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" s="14"/>
+      <c r="B150" s="16"/>
       <c r="C150" s="5" t="s">
         <v>37</v>
       </c>
@@ -8220,7 +8259,7 @@
       <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" s="14"/>
+      <c r="B151" s="16"/>
       <c r="C151" s="5" t="s">
         <v>38</v>
       </c>
@@ -8244,7 +8283,7 @@
       <c r="A152">
         <v>151</v>
       </c>
-      <c r="B152" s="14"/>
+      <c r="B152" s="16"/>
       <c r="C152" s="5" t="s">
         <v>39</v>
       </c>
@@ -8268,7 +8307,7 @@
       <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" s="14"/>
+      <c r="B153" s="16"/>
       <c r="C153" s="5" t="s">
         <v>40</v>
       </c>
@@ -8292,7 +8331,7 @@
       <c r="A154">
         <v>153</v>
       </c>
-      <c r="B154" s="14"/>
+      <c r="B154" s="16"/>
       <c r="C154" s="5" t="s">
         <v>41</v>
       </c>
@@ -8316,7 +8355,7 @@
       <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" s="14"/>
+      <c r="B155" s="16"/>
       <c r="C155" s="5" t="s">
         <v>36</v>
       </c>
@@ -8344,7 +8383,7 @@
       <c r="A156">
         <v>155</v>
       </c>
-      <c r="B156" s="14"/>
+      <c r="B156" s="16"/>
       <c r="C156" s="5" t="s">
         <v>37</v>
       </c>
@@ -8368,7 +8407,7 @@
       <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" s="14"/>
+      <c r="B157" s="16"/>
       <c r="C157" s="5" t="s">
         <v>38</v>
       </c>
@@ -8392,7 +8431,7 @@
       <c r="A158">
         <v>157</v>
       </c>
-      <c r="B158" s="14"/>
+      <c r="B158" s="16"/>
       <c r="C158" s="5" t="s">
         <v>39</v>
       </c>
@@ -8416,7 +8455,7 @@
       <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" s="14"/>
+      <c r="B159" s="16"/>
       <c r="C159" s="5" t="s">
         <v>40</v>
       </c>
@@ -8440,7 +8479,7 @@
       <c r="A160">
         <v>159</v>
       </c>
-      <c r="B160" s="14"/>
+      <c r="B160" s="16"/>
       <c r="C160" s="5" t="s">
         <v>41</v>
       </c>
@@ -8682,7 +8721,7 @@
       <c r="A170">
         <v>169</v>
       </c>
-      <c r="B170" s="14">
+      <c r="B170" s="16">
         <v>15</v>
       </c>
       <c r="C170" s="5" t="s">
@@ -8708,7 +8747,7 @@
       <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" s="14"/>
+      <c r="B171" s="16"/>
       <c r="C171" s="5" t="s">
         <v>40</v>
       </c>
@@ -8732,7 +8771,7 @@
       <c r="A172">
         <v>171</v>
       </c>
-      <c r="B172" s="14"/>
+      <c r="B172" s="16"/>
       <c r="C172" s="5" t="s">
         <v>41</v>
       </c>
@@ -8756,7 +8795,7 @@
       <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" s="14"/>
+      <c r="B173" s="16"/>
       <c r="C173" s="5" t="s">
         <v>36</v>
       </c>
@@ -8780,7 +8819,7 @@
       <c r="A174">
         <v>173</v>
       </c>
-      <c r="B174" s="14"/>
+      <c r="B174" s="16"/>
       <c r="C174" s="5" t="s">
         <v>37</v>
       </c>
@@ -8804,7 +8843,7 @@
       <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" s="14"/>
+      <c r="B175" s="16"/>
       <c r="C175" s="5" t="s">
         <v>38</v>
       </c>
@@ -8822,7 +8861,7 @@
       <c r="A176">
         <v>175</v>
       </c>
-      <c r="B176" s="14"/>
+      <c r="B176" s="16"/>
       <c r="C176" s="5" t="s">
         <v>39</v>
       </c>
@@ -8840,7 +8879,7 @@
       <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" s="14"/>
+      <c r="B177" s="16"/>
       <c r="C177" s="5" t="s">
         <v>40</v>
       </c>
@@ -8858,7 +8897,7 @@
       <c r="A178">
         <v>177</v>
       </c>
-      <c r="B178" s="14"/>
+      <c r="B178" s="16"/>
       <c r="C178" s="5" t="s">
         <v>41</v>
       </c>
@@ -9166,7 +9205,7 @@
       <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" s="14">
+      <c r="B191" s="16">
         <v>17</v>
       </c>
       <c r="C191" s="5" t="s">
@@ -9192,7 +9231,7 @@
       <c r="A192">
         <v>191</v>
       </c>
-      <c r="B192" s="14"/>
+      <c r="B192" s="16"/>
       <c r="C192" s="5" t="s">
         <v>37</v>
       </c>
@@ -9216,7 +9255,7 @@
       <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" s="14"/>
+      <c r="B193" s="16"/>
       <c r="C193" s="5" t="s">
         <v>38</v>
       </c>
@@ -9240,7 +9279,7 @@
       <c r="A194">
         <v>193</v>
       </c>
-      <c r="B194" s="14"/>
+      <c r="B194" s="16"/>
       <c r="C194" s="5" t="s">
         <v>39</v>
       </c>
@@ -9264,7 +9303,7 @@
       <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" s="14"/>
+      <c r="B195" s="16"/>
       <c r="C195" s="5" t="s">
         <v>40</v>
       </c>
@@ -9288,7 +9327,7 @@
       <c r="A196">
         <v>195</v>
       </c>
-      <c r="B196" s="14"/>
+      <c r="B196" s="16"/>
       <c r="C196" s="5" t="s">
         <v>41</v>
       </c>
@@ -9312,7 +9351,7 @@
       <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" s="14"/>
+      <c r="B197" s="16"/>
       <c r="C197" s="5" t="s">
         <v>36</v>
       </c>
@@ -9336,7 +9375,7 @@
       <c r="A198">
         <v>197</v>
       </c>
-      <c r="B198" s="14"/>
+      <c r="B198" s="16"/>
       <c r="C198" s="5" t="s">
         <v>37</v>
       </c>
@@ -9360,7 +9399,7 @@
       <c r="A199">
         <v>198</v>
       </c>
-      <c r="B199" s="14"/>
+      <c r="B199" s="16"/>
       <c r="C199" s="5" t="s">
         <v>38</v>
       </c>
@@ -9602,7 +9641,7 @@
       <c r="A209">
         <v>208</v>
       </c>
-      <c r="B209" s="14">
+      <c r="B209" s="16">
         <v>19</v>
       </c>
       <c r="C209" s="5" t="s">
@@ -9622,7 +9661,7 @@
       <c r="A210">
         <v>209</v>
       </c>
-      <c r="B210" s="14"/>
+      <c r="B210" s="16"/>
       <c r="C210" s="5" t="s">
         <v>37</v>
       </c>
@@ -9640,7 +9679,7 @@
       <c r="A211">
         <v>210</v>
       </c>
-      <c r="B211" s="14"/>
+      <c r="B211" s="16"/>
       <c r="C211" s="5" t="s">
         <v>38</v>
       </c>
@@ -9658,7 +9697,7 @@
       <c r="A212">
         <v>211</v>
       </c>
-      <c r="B212" s="14"/>
+      <c r="B212" s="16"/>
       <c r="C212" s="5" t="s">
         <v>39</v>
       </c>
@@ -9682,7 +9721,7 @@
       <c r="A213">
         <v>212</v>
       </c>
-      <c r="B213" s="14"/>
+      <c r="B213" s="16"/>
       <c r="C213" s="5" t="s">
         <v>40</v>
       </c>
@@ -9706,7 +9745,7 @@
       <c r="A214">
         <v>213</v>
       </c>
-      <c r="B214" s="14"/>
+      <c r="B214" s="16"/>
       <c r="C214" s="5" t="s">
         <v>41</v>
       </c>
@@ -9730,7 +9769,7 @@
       <c r="A215">
         <v>214</v>
       </c>
-      <c r="B215" s="14"/>
+      <c r="B215" s="16"/>
       <c r="C215" s="5" t="s">
         <v>42</v>
       </c>
@@ -9754,7 +9793,7 @@
       <c r="A216">
         <v>215</v>
       </c>
-      <c r="B216" s="14"/>
+      <c r="B216" s="16"/>
       <c r="C216" s="5" t="s">
         <v>43</v>
       </c>
@@ -9778,7 +9817,7 @@
       <c r="A217">
         <v>216</v>
       </c>
-      <c r="B217" s="14"/>
+      <c r="B217" s="16"/>
       <c r="C217" s="5" t="s">
         <v>44</v>
       </c>
@@ -9802,7 +9841,7 @@
       <c r="A218">
         <v>217</v>
       </c>
-      <c r="B218" s="14"/>
+      <c r="B218" s="16"/>
       <c r="C218" s="5" t="s">
         <v>45</v>
       </c>
@@ -9826,7 +9865,7 @@
       <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" s="14"/>
+      <c r="B219" s="16"/>
       <c r="C219" s="5" t="s">
         <v>46</v>
       </c>
@@ -9850,7 +9889,7 @@
       <c r="A220">
         <v>219</v>
       </c>
-      <c r="B220" s="14"/>
+      <c r="B220" s="16"/>
       <c r="C220" s="5" t="s">
         <v>47</v>
       </c>
@@ -9874,7 +9913,7 @@
       <c r="A221">
         <v>220</v>
       </c>
-      <c r="B221" s="14"/>
+      <c r="B221" s="16"/>
       <c r="C221" s="5" t="s">
         <v>48</v>
       </c>
@@ -9898,7 +9937,7 @@
       <c r="A222">
         <v>221</v>
       </c>
-      <c r="B222" s="14"/>
+      <c r="B222" s="16"/>
       <c r="C222" s="5" t="s">
         <v>36</v>
       </c>
@@ -9922,7 +9961,7 @@
       <c r="A223">
         <v>222</v>
       </c>
-      <c r="B223" s="14"/>
+      <c r="B223" s="16"/>
       <c r="C223" s="5" t="s">
         <v>37</v>
       </c>
@@ -9946,7 +9985,7 @@
       <c r="A224">
         <v>223</v>
       </c>
-      <c r="B224" s="14"/>
+      <c r="B224" s="16"/>
       <c r="C224" s="5" t="s">
         <v>38</v>
       </c>
@@ -9970,7 +10009,7 @@
       <c r="A225">
         <v>224</v>
       </c>
-      <c r="B225" s="14"/>
+      <c r="B225" s="16"/>
       <c r="C225" s="5" t="s">
         <v>49</v>
       </c>
@@ -9994,7 +10033,7 @@
       <c r="A226">
         <v>225</v>
       </c>
-      <c r="B226" s="14"/>
+      <c r="B226" s="16"/>
       <c r="C226" s="5" t="s">
         <v>50</v>
       </c>
@@ -10018,7 +10057,7 @@
       <c r="A227">
         <v>226</v>
       </c>
-      <c r="B227" s="14"/>
+      <c r="B227" s="16"/>
       <c r="C227" s="5" t="s">
         <v>51</v>
       </c>
@@ -10042,7 +10081,7 @@
       <c r="A228">
         <v>227</v>
       </c>
-      <c r="B228" s="14"/>
+      <c r="B228" s="16"/>
       <c r="C228" s="5" t="s">
         <v>52</v>
       </c>
@@ -10063,58 +10102,209 @@
       </c>
     </row>
     <row r="229" spans="1:8">
-      <c r="D229" t="s">
-        <v>54</v>
-      </c>
-      <c r="E229">
-        <f>MAX(E2:E228)</f>
-        <v>1.468</v>
-      </c>
-      <c r="F229">
-        <f t="shared" ref="F229:G229" si="0">MAX(F2:F228)</f>
-        <v>10.11</v>
-      </c>
-      <c r="G229">
-        <f t="shared" si="0"/>
-        <v>27.939</v>
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" s="18">
+        <v>20</v>
+      </c>
+      <c r="C229" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D229" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E229" s="19">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="F229" s="19">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G229" s="19">
+        <v>8.07</v>
+      </c>
+      <c r="H229" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="230" spans="1:8">
-      <c r="D230" t="s">
-        <v>55</v>
-      </c>
-      <c r="E230">
-        <f>MIN(E2:E228)</f>
-        <v>0.219</v>
-      </c>
-      <c r="F230">
-        <f t="shared" ref="F230:G230" si="1">MIN(F2:F228)</f>
-        <v>0.01</v>
-      </c>
-      <c r="G230">
-        <f t="shared" si="1"/>
-        <v>5.9560000000000004</v>
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" s="18"/>
+      <c r="C230" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D230" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E230" s="19">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="F230" s="19">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G230" s="19">
+        <v>8.31</v>
+      </c>
+      <c r="H230" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="231" spans="1:8">
-      <c r="D231" t="s">
-        <v>56</v>
-      </c>
-      <c r="E231" s="16">
-        <f>AVERAGE(E2:E228)</f>
-        <v>0.58585046728971923</v>
-      </c>
-      <c r="F231" s="16">
-        <f t="shared" ref="F231:G231" si="2">AVERAGE(F2:F228)</f>
-        <v>0.83742056074766358</v>
-      </c>
-      <c r="G231" s="16">
-        <f t="shared" si="2"/>
-        <v>12.438074766355133</v>
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" s="18"/>
+      <c r="C231" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D231" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E231" s="19">
+        <v>0.69</v>
+      </c>
+      <c r="F231" s="19">
+        <v>0.52</v>
+      </c>
+      <c r="G231" s="19">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="H231" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" s="18"/>
+      <c r="C232" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D232" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E232" s="19">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="F232" s="19">
+        <v>0.53</v>
+      </c>
+      <c r="G232" s="19">
+        <v>8.43</v>
+      </c>
+      <c r="H232" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" s="18"/>
+      <c r="C233" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D233" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E233" s="19">
+        <v>0.746</v>
+      </c>
+      <c r="F233" s="19">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G233" s="19">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="H233" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" s="18"/>
+      <c r="C234" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D234" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E234" s="19">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="F234" s="19">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G234" s="19">
+        <v>8.49</v>
+      </c>
+      <c r="H234" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" s="18"/>
+      <c r="C235" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D235" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E235" s="19">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="F235" s="19">
+        <v>0.53</v>
+      </c>
+      <c r="G235" s="19">
+        <v>8.14</v>
+      </c>
+      <c r="H235" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" s="18"/>
+      <c r="C236" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D236" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E236" s="19">
+        <v>0.73</v>
+      </c>
+      <c r="F236" s="19">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G236" s="19">
+        <v>8.57</v>
+      </c>
+      <c r="H236" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="B229:B236"/>
+    <mergeCell ref="B209:B228"/>
+    <mergeCell ref="B146:B160"/>
+    <mergeCell ref="B161:B169"/>
+    <mergeCell ref="B170:B178"/>
+    <mergeCell ref="B179:B190"/>
+    <mergeCell ref="B191:B199"/>
+    <mergeCell ref="B200:B208"/>
     <mergeCell ref="B128:B145"/>
     <mergeCell ref="B2:B13"/>
     <mergeCell ref="B14:B22"/>
@@ -10127,13 +10317,6 @@
     <mergeCell ref="B86:B97"/>
     <mergeCell ref="B98:B118"/>
     <mergeCell ref="B119:B127"/>
-    <mergeCell ref="B209:B228"/>
-    <mergeCell ref="B146:B160"/>
-    <mergeCell ref="B161:B169"/>
-    <mergeCell ref="B170:B178"/>
-    <mergeCell ref="B179:B190"/>
-    <mergeCell ref="B191:B199"/>
-    <mergeCell ref="B200:B208"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PRODUKSI/REPORT/LF_Ball_Mill_Metallurgical_Report.xlsx
+++ b/PRODUKSI/REPORT/LF_Ball_Mill_Metallurgical_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramda\Documents\Zeta_Edit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496E57BD-7A55-4A4F-B224-1C3F11CAC065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411F70A5-4552-449A-A4DF-D65884F1C81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="54">
   <si>
     <t>Periode</t>
   </si>
@@ -226,10 +226,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -249,6 +250,26 @@
     <font>
       <b/>
       <sz val="22"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -278,12 +299,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -306,11 +327,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -338,24 +396,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3453,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -4489,6 +4562,48 @@
       </c>
       <c r="E40">
         <v>8.41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B41">
+        <f>COUNT('Data Sampel'!D247:D264)</f>
+        <v>18</v>
+      </c>
+      <c r="C41" s="27">
+        <f>AVERAGE('Data Sampel'!E247:E264)</f>
+        <v>0.41022222222222227</v>
+      </c>
+      <c r="D41" s="27">
+        <f>AVERAGE('Data Sampel'!F247:F264)</f>
+        <v>0.34644444444444444</v>
+      </c>
+      <c r="E41" s="27">
+        <f>AVERAGE('Data Sampel'!G247:G264)</f>
+        <v>9.2982222222222219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B42">
+        <f>COUNT('Data Sampel'!D265:D269)</f>
+        <v>5</v>
+      </c>
+      <c r="C42" s="27">
+        <f>AVERAGE('Data Sampel'!E265:E269)</f>
+        <v>0.4446</v>
+      </c>
+      <c r="D42" s="27">
+        <f>AVERAGE('Data Sampel'!F265:F269)</f>
+        <v>0.46799999999999997</v>
+      </c>
+      <c r="E42" s="27">
+        <f>AVERAGE('Data Sampel'!G265:G269)</f>
+        <v>11.66</v>
       </c>
     </row>
   </sheetData>
@@ -4652,7 +4767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I236"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -4693,7 +4808,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="15">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -4719,7 +4834,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="5" t="s">
         <v>37</v>
       </c>
@@ -4743,7 +4858,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="5" t="s">
         <v>38</v>
       </c>
@@ -4767,7 +4882,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="5" t="s">
         <v>39</v>
       </c>
@@ -4791,7 +4906,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="15"/>
       <c r="C6" s="5" t="s">
         <v>40</v>
       </c>
@@ -4815,7 +4930,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="5" t="s">
         <v>41</v>
       </c>
@@ -4839,7 +4954,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="5" t="s">
         <v>36</v>
       </c>
@@ -4863,7 +4978,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="16"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
@@ -4887,7 +5002,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="16"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
@@ -4911,7 +5026,7 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="5" t="s">
         <v>39</v>
       </c>
@@ -4935,7 +5050,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="16"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
@@ -4959,7 +5074,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="5" t="s">
         <v>41</v>
       </c>
@@ -4983,7 +5098,7 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="16">
         <v>2</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -5009,7 +5124,7 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="7" t="s">
         <v>37</v>
       </c>
@@ -5033,7 +5148,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="15"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
@@ -5057,7 +5172,7 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="7" t="s">
         <v>39</v>
       </c>
@@ -5081,7 +5196,7 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="7" t="s">
         <v>40</v>
       </c>
@@ -5105,7 +5220,7 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="15"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="7" t="s">
         <v>41</v>
       </c>
@@ -5129,7 +5244,7 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="15"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="7" t="s">
         <v>36</v>
       </c>
@@ -5153,7 +5268,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="15"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="7" t="s">
         <v>37</v>
       </c>
@@ -5177,7 +5292,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="15"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
@@ -5201,7 +5316,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -5227,7 +5342,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="16"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="5" t="s">
         <v>40</v>
       </c>
@@ -5251,7 +5366,7 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="16"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="5" t="s">
         <v>41</v>
       </c>
@@ -5275,7 +5390,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="16"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="5" t="s">
         <v>36</v>
       </c>
@@ -5299,7 +5414,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="16"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="5" t="s">
         <v>37</v>
       </c>
@@ -5323,7 +5438,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="16"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="5" t="s">
         <v>38</v>
       </c>
@@ -5347,7 +5462,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="5" t="s">
         <v>39</v>
       </c>
@@ -5371,7 +5486,7 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="16"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
@@ -5395,7 +5510,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="16"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="5" t="s">
         <v>41</v>
       </c>
@@ -5419,7 +5534,7 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="16"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="5" t="s">
         <v>36</v>
       </c>
@@ -5443,7 +5558,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="16"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="5" t="s">
         <v>37</v>
       </c>
@@ -5467,7 +5582,7 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="16"/>
+      <c r="B34" s="15"/>
       <c r="C34" s="5" t="s">
         <v>38</v>
       </c>
@@ -5491,7 +5606,7 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="16">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -5517,7 +5632,7 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="15"/>
+      <c r="B36" s="16"/>
       <c r="C36" s="7" t="s">
         <v>40</v>
       </c>
@@ -5541,7 +5656,7 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="15"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="7" t="s">
         <v>41</v>
       </c>
@@ -5565,7 +5680,7 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="15"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="7" t="s">
         <v>36</v>
       </c>
@@ -5589,7 +5704,7 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="15"/>
+      <c r="B39" s="16"/>
       <c r="C39" s="7" t="s">
         <v>37</v>
       </c>
@@ -5613,7 +5728,7 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="15"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="7" t="s">
         <v>38</v>
       </c>
@@ -5637,7 +5752,7 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="15"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="7" t="s">
         <v>39</v>
       </c>
@@ -5661,7 +5776,7 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="15"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="7" t="s">
         <v>40</v>
       </c>
@@ -5685,7 +5800,7 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="15"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="7" t="s">
         <v>41</v>
       </c>
@@ -5709,7 +5824,7 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="15"/>
+      <c r="B44" s="16"/>
       <c r="C44" s="7" t="s">
         <v>36</v>
       </c>
@@ -5733,7 +5848,7 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="15"/>
+      <c r="B45" s="16"/>
       <c r="C45" s="7" t="s">
         <v>37</v>
       </c>
@@ -5757,7 +5872,7 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="15"/>
+      <c r="B46" s="16"/>
       <c r="C46" s="7" t="s">
         <v>38</v>
       </c>
@@ -5781,7 +5896,7 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="15"/>
+      <c r="B47" s="16"/>
       <c r="C47" s="7" t="s">
         <v>39</v>
       </c>
@@ -5799,7 +5914,7 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="15"/>
+      <c r="B48" s="16"/>
       <c r="C48" s="7" t="s">
         <v>40</v>
       </c>
@@ -5817,7 +5932,7 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="15"/>
+      <c r="B49" s="16"/>
       <c r="C49" s="7" t="s">
         <v>41</v>
       </c>
@@ -5835,7 +5950,7 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="15">
         <v>5</v>
       </c>
       <c r="C50" s="5" t="s">
@@ -5861,7 +5976,7 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="16"/>
+      <c r="B51" s="15"/>
       <c r="C51" s="5" t="s">
         <v>37</v>
       </c>
@@ -5885,7 +6000,7 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="16"/>
+      <c r="B52" s="15"/>
       <c r="C52" s="5" t="s">
         <v>38</v>
       </c>
@@ -5909,7 +6024,7 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="16"/>
+      <c r="B53" s="15"/>
       <c r="C53" s="5" t="s">
         <v>39</v>
       </c>
@@ -5933,7 +6048,7 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="16"/>
+      <c r="B54" s="15"/>
       <c r="C54" s="5" t="s">
         <v>40</v>
       </c>
@@ -5957,7 +6072,7 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="16"/>
+      <c r="B55" s="15"/>
       <c r="C55" s="5" t="s">
         <v>41</v>
       </c>
@@ -5981,7 +6096,7 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="16"/>
+      <c r="B56" s="15"/>
       <c r="C56" s="5" t="s">
         <v>36</v>
       </c>
@@ -6005,7 +6120,7 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="16"/>
+      <c r="B57" s="15"/>
       <c r="C57" s="5" t="s">
         <v>37</v>
       </c>
@@ -6029,7 +6144,7 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="16"/>
+      <c r="B58" s="15"/>
       <c r="C58" s="5" t="s">
         <v>38</v>
       </c>
@@ -6053,7 +6168,7 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="15">
+      <c r="B59" s="16">
         <v>6</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -6079,7 +6194,7 @@
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="15"/>
+      <c r="B60" s="16"/>
       <c r="C60" s="7" t="s">
         <v>40</v>
       </c>
@@ -6103,7 +6218,7 @@
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="15"/>
+      <c r="B61" s="16"/>
       <c r="C61" s="7" t="s">
         <v>41</v>
       </c>
@@ -6127,7 +6242,7 @@
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="15"/>
+      <c r="B62" s="16"/>
       <c r="C62" s="7" t="s">
         <v>36</v>
       </c>
@@ -6151,7 +6266,7 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="15"/>
+      <c r="B63" s="16"/>
       <c r="C63" s="7" t="s">
         <v>37</v>
       </c>
@@ -6175,7 +6290,7 @@
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="15"/>
+      <c r="B64" s="16"/>
       <c r="C64" s="7" t="s">
         <v>38</v>
       </c>
@@ -6199,7 +6314,7 @@
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="15">
         <v>7</v>
       </c>
       <c r="C65" s="5" t="s">
@@ -6225,7 +6340,7 @@
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="16"/>
+      <c r="B66" s="15"/>
       <c r="C66" s="5" t="s">
         <v>40</v>
       </c>
@@ -6249,7 +6364,7 @@
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="16"/>
+      <c r="B67" s="15"/>
       <c r="C67" s="5" t="s">
         <v>41</v>
       </c>
@@ -6273,7 +6388,7 @@
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="16"/>
+      <c r="B68" s="15"/>
       <c r="C68" s="5" t="s">
         <v>36</v>
       </c>
@@ -6297,7 +6412,7 @@
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="16"/>
+      <c r="B69" s="15"/>
       <c r="C69" s="5" t="s">
         <v>37</v>
       </c>
@@ -6321,7 +6436,7 @@
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="16"/>
+      <c r="B70" s="15"/>
       <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
@@ -6345,7 +6460,7 @@
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="16"/>
+      <c r="B71" s="15"/>
       <c r="C71" s="5" t="s">
         <v>39</v>
       </c>
@@ -6369,7 +6484,7 @@
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="16"/>
+      <c r="B72" s="15"/>
       <c r="C72" s="5" t="s">
         <v>40</v>
       </c>
@@ -6393,7 +6508,7 @@
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="16"/>
+      <c r="B73" s="15"/>
       <c r="C73" s="5" t="s">
         <v>41</v>
       </c>
@@ -6417,7 +6532,7 @@
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="15">
+      <c r="B74" s="16">
         <v>8</v>
       </c>
       <c r="C74" s="7" t="s">
@@ -6443,7 +6558,7 @@
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="15"/>
+      <c r="B75" s="16"/>
       <c r="C75" s="7" t="s">
         <v>37</v>
       </c>
@@ -6467,7 +6582,7 @@
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="15"/>
+      <c r="B76" s="16"/>
       <c r="C76" s="7" t="s">
         <v>38</v>
       </c>
@@ -6491,7 +6606,7 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="15"/>
+      <c r="B77" s="16"/>
       <c r="C77" s="7" t="s">
         <v>39</v>
       </c>
@@ -6515,7 +6630,7 @@
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="15"/>
+      <c r="B78" s="16"/>
       <c r="C78" s="7" t="s">
         <v>40</v>
       </c>
@@ -6539,7 +6654,7 @@
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="15"/>
+      <c r="B79" s="16"/>
       <c r="C79" s="7" t="s">
         <v>41</v>
       </c>
@@ -6563,7 +6678,7 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="15"/>
+      <c r="B80" s="16"/>
       <c r="C80" s="7" t="s">
         <v>36</v>
       </c>
@@ -6587,7 +6702,7 @@
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="15"/>
+      <c r="B81" s="16"/>
       <c r="C81" s="7" t="s">
         <v>37</v>
       </c>
@@ -6611,7 +6726,7 @@
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="15"/>
+      <c r="B82" s="16"/>
       <c r="C82" s="7" t="s">
         <v>38</v>
       </c>
@@ -6635,7 +6750,7 @@
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="15"/>
+      <c r="B83" s="16"/>
       <c r="C83" s="7" t="s">
         <v>39</v>
       </c>
@@ -6659,7 +6774,7 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="15"/>
+      <c r="B84" s="16"/>
       <c r="C84" s="7" t="s">
         <v>40</v>
       </c>
@@ -6683,7 +6798,7 @@
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="15"/>
+      <c r="B85" s="16"/>
       <c r="C85" s="7" t="s">
         <v>41</v>
       </c>
@@ -6707,7 +6822,7 @@
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="15">
         <v>9</v>
       </c>
       <c r="C86" s="5" t="s">
@@ -6733,7 +6848,7 @@
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="16"/>
+      <c r="B87" s="15"/>
       <c r="C87" s="5" t="s">
         <v>37</v>
       </c>
@@ -6757,7 +6872,7 @@
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="16"/>
+      <c r="B88" s="15"/>
       <c r="C88" s="5" t="s">
         <v>38</v>
       </c>
@@ -6781,7 +6896,7 @@
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="16"/>
+      <c r="B89" s="15"/>
       <c r="C89" s="5" t="s">
         <v>39</v>
       </c>
@@ -6805,7 +6920,7 @@
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="16"/>
+      <c r="B90" s="15"/>
       <c r="C90" s="5" t="s">
         <v>40</v>
       </c>
@@ -6829,7 +6944,7 @@
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="16"/>
+      <c r="B91" s="15"/>
       <c r="C91" s="5" t="s">
         <v>41</v>
       </c>
@@ -6853,7 +6968,7 @@
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="16"/>
+      <c r="B92" s="15"/>
       <c r="C92" s="5" t="s">
         <v>36</v>
       </c>
@@ -6877,7 +6992,7 @@
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="16"/>
+      <c r="B93" s="15"/>
       <c r="C93" s="5" t="s">
         <v>37</v>
       </c>
@@ -6901,7 +7016,7 @@
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="16"/>
+      <c r="B94" s="15"/>
       <c r="C94" s="5" t="s">
         <v>38</v>
       </c>
@@ -6925,7 +7040,7 @@
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="16"/>
+      <c r="B95" s="15"/>
       <c r="C95" s="5" t="s">
         <v>39</v>
       </c>
@@ -6949,7 +7064,7 @@
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="16"/>
+      <c r="B96" s="15"/>
       <c r="C96" s="5" t="s">
         <v>40</v>
       </c>
@@ -6973,7 +7088,7 @@
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="16"/>
+      <c r="B97" s="15"/>
       <c r="C97" s="5" t="s">
         <v>41</v>
       </c>
@@ -6997,7 +7112,7 @@
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" s="15">
+      <c r="B98" s="16">
         <v>10</v>
       </c>
       <c r="C98" s="7" t="s">
@@ -7023,7 +7138,7 @@
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" s="15"/>
+      <c r="B99" s="16"/>
       <c r="C99" s="7" t="s">
         <v>37</v>
       </c>
@@ -7047,7 +7162,7 @@
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" s="15"/>
+      <c r="B100" s="16"/>
       <c r="C100" s="7" t="s">
         <v>38</v>
       </c>
@@ -7071,7 +7186,7 @@
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" s="15"/>
+      <c r="B101" s="16"/>
       <c r="C101" s="7" t="s">
         <v>39</v>
       </c>
@@ -7095,7 +7210,7 @@
       <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" s="15"/>
+      <c r="B102" s="16"/>
       <c r="C102" s="7" t="s">
         <v>40</v>
       </c>
@@ -7119,7 +7234,7 @@
       <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" s="15"/>
+      <c r="B103" s="16"/>
       <c r="C103" s="7" t="s">
         <v>41</v>
       </c>
@@ -7143,7 +7258,7 @@
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" s="15"/>
+      <c r="B104" s="16"/>
       <c r="C104" s="7" t="s">
         <v>36</v>
       </c>
@@ -7167,7 +7282,7 @@
       <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" s="15"/>
+      <c r="B105" s="16"/>
       <c r="C105" s="7" t="s">
         <v>37</v>
       </c>
@@ -7191,7 +7306,7 @@
       <c r="A106">
         <v>105</v>
       </c>
-      <c r="B106" s="15"/>
+      <c r="B106" s="16"/>
       <c r="C106" s="7" t="s">
         <v>38</v>
       </c>
@@ -7215,7 +7330,7 @@
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="15"/>
+      <c r="B107" s="16"/>
       <c r="C107" s="7" t="s">
         <v>39</v>
       </c>
@@ -7239,7 +7354,7 @@
       <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" s="15"/>
+      <c r="B108" s="16"/>
       <c r="C108" s="7" t="s">
         <v>40</v>
       </c>
@@ -7263,7 +7378,7 @@
       <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" s="15"/>
+      <c r="B109" s="16"/>
       <c r="C109" s="7" t="s">
         <v>41</v>
       </c>
@@ -7287,7 +7402,7 @@
       <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" s="15"/>
+      <c r="B110" s="16"/>
       <c r="C110" s="7" t="s">
         <v>36</v>
       </c>
@@ -7311,7 +7426,7 @@
       <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" s="15"/>
+      <c r="B111" s="16"/>
       <c r="C111" s="7" t="s">
         <v>37</v>
       </c>
@@ -7335,7 +7450,7 @@
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" s="15"/>
+      <c r="B112" s="16"/>
       <c r="C112" s="7" t="s">
         <v>38</v>
       </c>
@@ -7359,7 +7474,7 @@
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" s="15"/>
+      <c r="B113" s="16"/>
       <c r="C113" s="7" t="s">
         <v>39</v>
       </c>
@@ -7383,7 +7498,7 @@
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" s="15"/>
+      <c r="B114" s="16"/>
       <c r="C114" s="7" t="s">
         <v>40</v>
       </c>
@@ -7407,7 +7522,7 @@
       <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" s="15"/>
+      <c r="B115" s="16"/>
       <c r="C115" s="7" t="s">
         <v>41</v>
       </c>
@@ -7431,7 +7546,7 @@
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" s="15"/>
+      <c r="B116" s="16"/>
       <c r="C116" s="7" t="s">
         <v>36</v>
       </c>
@@ -7455,7 +7570,7 @@
       <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" s="15"/>
+      <c r="B117" s="16"/>
       <c r="C117" s="7" t="s">
         <v>37</v>
       </c>
@@ -7479,7 +7594,7 @@
       <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" s="15"/>
+      <c r="B118" s="16"/>
       <c r="C118" s="7" t="s">
         <v>38</v>
       </c>
@@ -7503,7 +7618,7 @@
       <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B119" s="15">
         <v>11</v>
       </c>
       <c r="C119" s="5" t="s">
@@ -7529,7 +7644,7 @@
       <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" s="16"/>
+      <c r="B120" s="15"/>
       <c r="C120" s="5" t="s">
         <v>40</v>
       </c>
@@ -7553,7 +7668,7 @@
       <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" s="16"/>
+      <c r="B121" s="15"/>
       <c r="C121" s="5" t="s">
         <v>41</v>
       </c>
@@ -7577,7 +7692,7 @@
       <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" s="16"/>
+      <c r="B122" s="15"/>
       <c r="C122" s="5" t="s">
         <v>36</v>
       </c>
@@ -7601,7 +7716,7 @@
       <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" s="16"/>
+      <c r="B123" s="15"/>
       <c r="C123" s="5" t="s">
         <v>37</v>
       </c>
@@ -7625,7 +7740,7 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" s="16"/>
+      <c r="B124" s="15"/>
       <c r="C124" s="5" t="s">
         <v>38</v>
       </c>
@@ -7649,7 +7764,7 @@
       <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" s="16"/>
+      <c r="B125" s="15"/>
       <c r="C125" s="5" t="s">
         <v>39</v>
       </c>
@@ -7667,7 +7782,7 @@
       <c r="A126">
         <v>125</v>
       </c>
-      <c r="B126" s="16"/>
+      <c r="B126" s="15"/>
       <c r="C126" s="5" t="s">
         <v>40</v>
       </c>
@@ -7685,7 +7800,7 @@
       <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" s="16"/>
+      <c r="B127" s="15"/>
       <c r="C127" s="5" t="s">
         <v>41</v>
       </c>
@@ -7703,7 +7818,7 @@
       <c r="A128">
         <v>127</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B128" s="16">
         <v>12</v>
       </c>
       <c r="C128" s="7" t="s">
@@ -7729,7 +7844,7 @@
       <c r="A129">
         <v>128</v>
       </c>
-      <c r="B129" s="15"/>
+      <c r="B129" s="16"/>
       <c r="C129" s="7" t="s">
         <v>37</v>
       </c>
@@ -7753,7 +7868,7 @@
       <c r="A130">
         <v>129</v>
       </c>
-      <c r="B130" s="15"/>
+      <c r="B130" s="16"/>
       <c r="C130" s="7" t="s">
         <v>38</v>
       </c>
@@ -7777,7 +7892,7 @@
       <c r="A131">
         <v>130</v>
       </c>
-      <c r="B131" s="15"/>
+      <c r="B131" s="16"/>
       <c r="C131" s="7" t="s">
         <v>39</v>
       </c>
@@ -7801,7 +7916,7 @@
       <c r="A132">
         <v>131</v>
       </c>
-      <c r="B132" s="15"/>
+      <c r="B132" s="16"/>
       <c r="C132" s="7" t="s">
         <v>40</v>
       </c>
@@ -7825,7 +7940,7 @@
       <c r="A133">
         <v>132</v>
       </c>
-      <c r="B133" s="15"/>
+      <c r="B133" s="16"/>
       <c r="C133" s="7" t="s">
         <v>41</v>
       </c>
@@ -7849,7 +7964,7 @@
       <c r="A134">
         <v>133</v>
       </c>
-      <c r="B134" s="15"/>
+      <c r="B134" s="16"/>
       <c r="C134" s="7" t="s">
         <v>36</v>
       </c>
@@ -7873,7 +7988,7 @@
       <c r="A135">
         <v>134</v>
       </c>
-      <c r="B135" s="15"/>
+      <c r="B135" s="16"/>
       <c r="C135" s="7" t="s">
         <v>37</v>
       </c>
@@ -7897,7 +8012,7 @@
       <c r="A136">
         <v>135</v>
       </c>
-      <c r="B136" s="15"/>
+      <c r="B136" s="16"/>
       <c r="C136" s="7" t="s">
         <v>38</v>
       </c>
@@ -7921,7 +8036,7 @@
       <c r="A137">
         <v>136</v>
       </c>
-      <c r="B137" s="15"/>
+      <c r="B137" s="16"/>
       <c r="C137" s="7" t="s">
         <v>39</v>
       </c>
@@ -7945,7 +8060,7 @@
       <c r="A138">
         <v>137</v>
       </c>
-      <c r="B138" s="15"/>
+      <c r="B138" s="16"/>
       <c r="C138" s="7" t="s">
         <v>40</v>
       </c>
@@ -7969,7 +8084,7 @@
       <c r="A139">
         <v>138</v>
       </c>
-      <c r="B139" s="15"/>
+      <c r="B139" s="16"/>
       <c r="C139" s="7" t="s">
         <v>41</v>
       </c>
@@ -7993,7 +8108,7 @@
       <c r="A140">
         <v>139</v>
       </c>
-      <c r="B140" s="15"/>
+      <c r="B140" s="16"/>
       <c r="C140" s="7" t="s">
         <v>36</v>
       </c>
@@ -8017,7 +8132,7 @@
       <c r="A141">
         <v>140</v>
       </c>
-      <c r="B141" s="15"/>
+      <c r="B141" s="16"/>
       <c r="C141" s="7" t="s">
         <v>37</v>
       </c>
@@ -8041,7 +8156,7 @@
       <c r="A142">
         <v>141</v>
       </c>
-      <c r="B142" s="15"/>
+      <c r="B142" s="16"/>
       <c r="C142" s="7" t="s">
         <v>38</v>
       </c>
@@ -8065,7 +8180,7 @@
       <c r="A143">
         <v>142</v>
       </c>
-      <c r="B143" s="15"/>
+      <c r="B143" s="16"/>
       <c r="C143" s="7" t="s">
         <v>39</v>
       </c>
@@ -8089,7 +8204,7 @@
       <c r="A144">
         <v>143</v>
       </c>
-      <c r="B144" s="15"/>
+      <c r="B144" s="16"/>
       <c r="C144" s="7" t="s">
         <v>40</v>
       </c>
@@ -8113,7 +8228,7 @@
       <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" s="15"/>
+      <c r="B145" s="16"/>
       <c r="C145" s="7" t="s">
         <v>41</v>
       </c>
@@ -8137,7 +8252,7 @@
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="15">
         <v>13</v>
       </c>
       <c r="C146" s="5" t="s">
@@ -8163,7 +8278,7 @@
       <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" s="16"/>
+      <c r="B147" s="15"/>
       <c r="C147" s="5" t="s">
         <v>40</v>
       </c>
@@ -8187,7 +8302,7 @@
       <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" s="16"/>
+      <c r="B148" s="15"/>
       <c r="C148" s="5" t="s">
         <v>41</v>
       </c>
@@ -8211,7 +8326,7 @@
       <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" s="16"/>
+      <c r="B149" s="15"/>
       <c r="C149" s="5" t="s">
         <v>36</v>
       </c>
@@ -8235,7 +8350,7 @@
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" s="16"/>
+      <c r="B150" s="15"/>
       <c r="C150" s="5" t="s">
         <v>37</v>
       </c>
@@ -8259,7 +8374,7 @@
       <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" s="16"/>
+      <c r="B151" s="15"/>
       <c r="C151" s="5" t="s">
         <v>38</v>
       </c>
@@ -8283,7 +8398,7 @@
       <c r="A152">
         <v>151</v>
       </c>
-      <c r="B152" s="16"/>
+      <c r="B152" s="15"/>
       <c r="C152" s="5" t="s">
         <v>39</v>
       </c>
@@ -8307,7 +8422,7 @@
       <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" s="16"/>
+      <c r="B153" s="15"/>
       <c r="C153" s="5" t="s">
         <v>40</v>
       </c>
@@ -8331,7 +8446,7 @@
       <c r="A154">
         <v>153</v>
       </c>
-      <c r="B154" s="16"/>
+      <c r="B154" s="15"/>
       <c r="C154" s="5" t="s">
         <v>41</v>
       </c>
@@ -8355,7 +8470,7 @@
       <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" s="16"/>
+      <c r="B155" s="15"/>
       <c r="C155" s="5" t="s">
         <v>36</v>
       </c>
@@ -8383,7 +8498,7 @@
       <c r="A156">
         <v>155</v>
       </c>
-      <c r="B156" s="16"/>
+      <c r="B156" s="15"/>
       <c r="C156" s="5" t="s">
         <v>37</v>
       </c>
@@ -8407,7 +8522,7 @@
       <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" s="16"/>
+      <c r="B157" s="15"/>
       <c r="C157" s="5" t="s">
         <v>38</v>
       </c>
@@ -8431,7 +8546,7 @@
       <c r="A158">
         <v>157</v>
       </c>
-      <c r="B158" s="16"/>
+      <c r="B158" s="15"/>
       <c r="C158" s="5" t="s">
         <v>39</v>
       </c>
@@ -8455,7 +8570,7 @@
       <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" s="16"/>
+      <c r="B159" s="15"/>
       <c r="C159" s="5" t="s">
         <v>40</v>
       </c>
@@ -8479,7 +8594,7 @@
       <c r="A160">
         <v>159</v>
       </c>
-      <c r="B160" s="16"/>
+      <c r="B160" s="15"/>
       <c r="C160" s="5" t="s">
         <v>41</v>
       </c>
@@ -8503,7 +8618,7 @@
       <c r="A161">
         <v>160</v>
       </c>
-      <c r="B161" s="15">
+      <c r="B161" s="16">
         <v>14</v>
       </c>
       <c r="C161" s="7" t="s">
@@ -8529,7 +8644,7 @@
       <c r="A162">
         <v>161</v>
       </c>
-      <c r="B162" s="15"/>
+      <c r="B162" s="16"/>
       <c r="C162" s="7" t="s">
         <v>37</v>
       </c>
@@ -8553,7 +8668,7 @@
       <c r="A163">
         <v>162</v>
       </c>
-      <c r="B163" s="15"/>
+      <c r="B163" s="16"/>
       <c r="C163" s="7" t="s">
         <v>38</v>
       </c>
@@ -8577,7 +8692,7 @@
       <c r="A164">
         <v>163</v>
       </c>
-      <c r="B164" s="15"/>
+      <c r="B164" s="16"/>
       <c r="C164" s="7" t="s">
         <v>39</v>
       </c>
@@ -8601,7 +8716,7 @@
       <c r="A165">
         <v>164</v>
       </c>
-      <c r="B165" s="15"/>
+      <c r="B165" s="16"/>
       <c r="C165" s="7" t="s">
         <v>40</v>
       </c>
@@ -8625,7 +8740,7 @@
       <c r="A166">
         <v>165</v>
       </c>
-      <c r="B166" s="15"/>
+      <c r="B166" s="16"/>
       <c r="C166" s="7" t="s">
         <v>41</v>
       </c>
@@ -8649,7 +8764,7 @@
       <c r="A167">
         <v>166</v>
       </c>
-      <c r="B167" s="15"/>
+      <c r="B167" s="16"/>
       <c r="C167" s="7" t="s">
         <v>36</v>
       </c>
@@ -8673,7 +8788,7 @@
       <c r="A168">
         <v>167</v>
       </c>
-      <c r="B168" s="15"/>
+      <c r="B168" s="16"/>
       <c r="C168" s="7" t="s">
         <v>37</v>
       </c>
@@ -8697,7 +8812,7 @@
       <c r="A169">
         <v>168</v>
       </c>
-      <c r="B169" s="15"/>
+      <c r="B169" s="16"/>
       <c r="C169" s="7" t="s">
         <v>38</v>
       </c>
@@ -8721,7 +8836,7 @@
       <c r="A170">
         <v>169</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="15">
         <v>15</v>
       </c>
       <c r="C170" s="5" t="s">
@@ -8747,7 +8862,7 @@
       <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" s="16"/>
+      <c r="B171" s="15"/>
       <c r="C171" s="5" t="s">
         <v>40</v>
       </c>
@@ -8771,7 +8886,7 @@
       <c r="A172">
         <v>171</v>
       </c>
-      <c r="B172" s="16"/>
+      <c r="B172" s="15"/>
       <c r="C172" s="5" t="s">
         <v>41</v>
       </c>
@@ -8795,7 +8910,7 @@
       <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" s="16"/>
+      <c r="B173" s="15"/>
       <c r="C173" s="5" t="s">
         <v>36</v>
       </c>
@@ -8819,7 +8934,7 @@
       <c r="A174">
         <v>173</v>
       </c>
-      <c r="B174" s="16"/>
+      <c r="B174" s="15"/>
       <c r="C174" s="5" t="s">
         <v>37</v>
       </c>
@@ -8843,7 +8958,7 @@
       <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" s="16"/>
+      <c r="B175" s="15"/>
       <c r="C175" s="5" t="s">
         <v>38</v>
       </c>
@@ -8861,7 +8976,7 @@
       <c r="A176">
         <v>175</v>
       </c>
-      <c r="B176" s="16"/>
+      <c r="B176" s="15"/>
       <c r="C176" s="5" t="s">
         <v>39</v>
       </c>
@@ -8879,7 +8994,7 @@
       <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" s="16"/>
+      <c r="B177" s="15"/>
       <c r="C177" s="5" t="s">
         <v>40</v>
       </c>
@@ -8897,7 +9012,7 @@
       <c r="A178">
         <v>177</v>
       </c>
-      <c r="B178" s="16"/>
+      <c r="B178" s="15"/>
       <c r="C178" s="5" t="s">
         <v>41</v>
       </c>
@@ -8915,7 +9030,7 @@
       <c r="A179">
         <v>178</v>
       </c>
-      <c r="B179" s="15">
+      <c r="B179" s="16">
         <v>16</v>
       </c>
       <c r="C179" s="7" t="s">
@@ -8941,7 +9056,7 @@
       <c r="A180">
         <v>179</v>
       </c>
-      <c r="B180" s="15"/>
+      <c r="B180" s="16"/>
       <c r="C180" s="7" t="s">
         <v>40</v>
       </c>
@@ -8965,7 +9080,7 @@
       <c r="A181">
         <v>180</v>
       </c>
-      <c r="B181" s="15"/>
+      <c r="B181" s="16"/>
       <c r="C181" s="7" t="s">
         <v>41</v>
       </c>
@@ -8989,7 +9104,7 @@
       <c r="A182">
         <v>181</v>
       </c>
-      <c r="B182" s="15"/>
+      <c r="B182" s="16"/>
       <c r="C182" s="7" t="s">
         <v>36</v>
       </c>
@@ -9013,7 +9128,7 @@
       <c r="A183">
         <v>182</v>
       </c>
-      <c r="B183" s="15"/>
+      <c r="B183" s="16"/>
       <c r="C183" s="7" t="s">
         <v>37</v>
       </c>
@@ -9037,7 +9152,7 @@
       <c r="A184">
         <v>183</v>
       </c>
-      <c r="B184" s="15"/>
+      <c r="B184" s="16"/>
       <c r="C184" s="7" t="s">
         <v>38</v>
       </c>
@@ -9061,7 +9176,7 @@
       <c r="A185">
         <v>184</v>
       </c>
-      <c r="B185" s="15"/>
+      <c r="B185" s="16"/>
       <c r="C185" s="7" t="s">
         <v>39</v>
       </c>
@@ -9085,7 +9200,7 @@
       <c r="A186">
         <v>185</v>
       </c>
-      <c r="B186" s="15"/>
+      <c r="B186" s="16"/>
       <c r="C186" s="7" t="s">
         <v>40</v>
       </c>
@@ -9109,7 +9224,7 @@
       <c r="A187">
         <v>186</v>
       </c>
-      <c r="B187" s="15"/>
+      <c r="B187" s="16"/>
       <c r="C187" s="7" t="s">
         <v>41</v>
       </c>
@@ -9133,7 +9248,7 @@
       <c r="A188">
         <v>187</v>
       </c>
-      <c r="B188" s="15"/>
+      <c r="B188" s="16"/>
       <c r="C188" s="7" t="s">
         <v>36</v>
       </c>
@@ -9157,7 +9272,7 @@
       <c r="A189">
         <v>188</v>
       </c>
-      <c r="B189" s="15"/>
+      <c r="B189" s="16"/>
       <c r="C189" s="7" t="s">
         <v>37</v>
       </c>
@@ -9181,7 +9296,7 @@
       <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" s="15"/>
+      <c r="B190" s="16"/>
       <c r="C190" s="7" t="s">
         <v>38</v>
       </c>
@@ -9205,7 +9320,7 @@
       <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" s="16">
+      <c r="B191" s="15">
         <v>17</v>
       </c>
       <c r="C191" s="5" t="s">
@@ -9231,7 +9346,7 @@
       <c r="A192">
         <v>191</v>
       </c>
-      <c r="B192" s="16"/>
+      <c r="B192" s="15"/>
       <c r="C192" s="5" t="s">
         <v>37</v>
       </c>
@@ -9255,7 +9370,7 @@
       <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" s="16"/>
+      <c r="B193" s="15"/>
       <c r="C193" s="5" t="s">
         <v>38</v>
       </c>
@@ -9279,7 +9394,7 @@
       <c r="A194">
         <v>193</v>
       </c>
-      <c r="B194" s="16"/>
+      <c r="B194" s="15"/>
       <c r="C194" s="5" t="s">
         <v>39</v>
       </c>
@@ -9303,7 +9418,7 @@
       <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" s="16"/>
+      <c r="B195" s="15"/>
       <c r="C195" s="5" t="s">
         <v>40</v>
       </c>
@@ -9327,7 +9442,7 @@
       <c r="A196">
         <v>195</v>
       </c>
-      <c r="B196" s="16"/>
+      <c r="B196" s="15"/>
       <c r="C196" s="5" t="s">
         <v>41</v>
       </c>
@@ -9351,7 +9466,7 @@
       <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" s="16"/>
+      <c r="B197" s="15"/>
       <c r="C197" s="5" t="s">
         <v>36</v>
       </c>
@@ -9375,7 +9490,7 @@
       <c r="A198">
         <v>197</v>
       </c>
-      <c r="B198" s="16"/>
+      <c r="B198" s="15"/>
       <c r="C198" s="5" t="s">
         <v>37</v>
       </c>
@@ -9399,7 +9514,7 @@
       <c r="A199">
         <v>198</v>
       </c>
-      <c r="B199" s="16"/>
+      <c r="B199" s="15"/>
       <c r="C199" s="5" t="s">
         <v>38</v>
       </c>
@@ -9423,7 +9538,7 @@
       <c r="A200">
         <v>199</v>
       </c>
-      <c r="B200" s="15">
+      <c r="B200" s="16">
         <v>18</v>
       </c>
       <c r="C200" s="7" t="s">
@@ -9449,7 +9564,7 @@
       <c r="A201">
         <v>200</v>
       </c>
-      <c r="B201" s="15"/>
+      <c r="B201" s="16"/>
       <c r="C201" s="7" t="s">
         <v>40</v>
       </c>
@@ -9473,7 +9588,7 @@
       <c r="A202">
         <v>201</v>
       </c>
-      <c r="B202" s="15"/>
+      <c r="B202" s="16"/>
       <c r="C202" s="7" t="s">
         <v>41</v>
       </c>
@@ -9497,7 +9612,7 @@
       <c r="A203">
         <v>202</v>
       </c>
-      <c r="B203" s="15"/>
+      <c r="B203" s="16"/>
       <c r="C203" s="7" t="s">
         <v>36</v>
       </c>
@@ -9521,7 +9636,7 @@
       <c r="A204">
         <v>203</v>
       </c>
-      <c r="B204" s="15"/>
+      <c r="B204" s="16"/>
       <c r="C204" s="7" t="s">
         <v>37</v>
       </c>
@@ -9545,7 +9660,7 @@
       <c r="A205">
         <v>204</v>
       </c>
-      <c r="B205" s="15"/>
+      <c r="B205" s="16"/>
       <c r="C205" s="7" t="s">
         <v>38</v>
       </c>
@@ -9569,7 +9684,7 @@
       <c r="A206">
         <v>205</v>
       </c>
-      <c r="B206" s="15"/>
+      <c r="B206" s="16"/>
       <c r="C206" s="7" t="s">
         <v>39</v>
       </c>
@@ -9593,7 +9708,7 @@
       <c r="A207">
         <v>206</v>
       </c>
-      <c r="B207" s="15"/>
+      <c r="B207" s="16"/>
       <c r="C207" s="7" t="s">
         <v>40</v>
       </c>
@@ -9617,7 +9732,7 @@
       <c r="A208">
         <v>207</v>
       </c>
-      <c r="B208" s="15"/>
+      <c r="B208" s="16"/>
       <c r="C208" s="7" t="s">
         <v>41</v>
       </c>
@@ -9641,7 +9756,7 @@
       <c r="A209">
         <v>208</v>
       </c>
-      <c r="B209" s="16">
+      <c r="B209" s="15">
         <v>19</v>
       </c>
       <c r="C209" s="5" t="s">
@@ -9661,7 +9776,7 @@
       <c r="A210">
         <v>209</v>
       </c>
-      <c r="B210" s="16"/>
+      <c r="B210" s="15"/>
       <c r="C210" s="5" t="s">
         <v>37</v>
       </c>
@@ -9679,7 +9794,7 @@
       <c r="A211">
         <v>210</v>
       </c>
-      <c r="B211" s="16"/>
+      <c r="B211" s="15"/>
       <c r="C211" s="5" t="s">
         <v>38</v>
       </c>
@@ -9697,7 +9812,7 @@
       <c r="A212">
         <v>211</v>
       </c>
-      <c r="B212" s="16"/>
+      <c r="B212" s="15"/>
       <c r="C212" s="5" t="s">
         <v>39</v>
       </c>
@@ -9721,7 +9836,7 @@
       <c r="A213">
         <v>212</v>
       </c>
-      <c r="B213" s="16"/>
+      <c r="B213" s="15"/>
       <c r="C213" s="5" t="s">
         <v>40</v>
       </c>
@@ -9745,7 +9860,7 @@
       <c r="A214">
         <v>213</v>
       </c>
-      <c r="B214" s="16"/>
+      <c r="B214" s="15"/>
       <c r="C214" s="5" t="s">
         <v>41</v>
       </c>
@@ -9769,7 +9884,7 @@
       <c r="A215">
         <v>214</v>
       </c>
-      <c r="B215" s="16"/>
+      <c r="B215" s="15"/>
       <c r="C215" s="5" t="s">
         <v>42</v>
       </c>
@@ -9793,7 +9908,7 @@
       <c r="A216">
         <v>215</v>
       </c>
-      <c r="B216" s="16"/>
+      <c r="B216" s="15"/>
       <c r="C216" s="5" t="s">
         <v>43</v>
       </c>
@@ -9817,7 +9932,7 @@
       <c r="A217">
         <v>216</v>
       </c>
-      <c r="B217" s="16"/>
+      <c r="B217" s="15"/>
       <c r="C217" s="5" t="s">
         <v>44</v>
       </c>
@@ -9841,7 +9956,7 @@
       <c r="A218">
         <v>217</v>
       </c>
-      <c r="B218" s="16"/>
+      <c r="B218" s="15"/>
       <c r="C218" s="5" t="s">
         <v>45</v>
       </c>
@@ -9865,7 +9980,7 @@
       <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" s="16"/>
+      <c r="B219" s="15"/>
       <c r="C219" s="5" t="s">
         <v>46</v>
       </c>
@@ -9889,7 +10004,7 @@
       <c r="A220">
         <v>219</v>
       </c>
-      <c r="B220" s="16"/>
+      <c r="B220" s="15"/>
       <c r="C220" s="5" t="s">
         <v>47</v>
       </c>
@@ -9913,7 +10028,7 @@
       <c r="A221">
         <v>220</v>
       </c>
-      <c r="B221" s="16"/>
+      <c r="B221" s="15"/>
       <c r="C221" s="5" t="s">
         <v>48</v>
       </c>
@@ -9937,7 +10052,7 @@
       <c r="A222">
         <v>221</v>
       </c>
-      <c r="B222" s="16"/>
+      <c r="B222" s="15"/>
       <c r="C222" s="5" t="s">
         <v>36</v>
       </c>
@@ -9961,7 +10076,7 @@
       <c r="A223">
         <v>222</v>
       </c>
-      <c r="B223" s="16"/>
+      <c r="B223" s="15"/>
       <c r="C223" s="5" t="s">
         <v>37</v>
       </c>
@@ -9985,7 +10100,7 @@
       <c r="A224">
         <v>223</v>
       </c>
-      <c r="B224" s="16"/>
+      <c r="B224" s="15"/>
       <c r="C224" s="5" t="s">
         <v>38</v>
       </c>
@@ -10009,7 +10124,7 @@
       <c r="A225">
         <v>224</v>
       </c>
-      <c r="B225" s="16"/>
+      <c r="B225" s="15"/>
       <c r="C225" s="5" t="s">
         <v>49</v>
       </c>
@@ -10033,7 +10148,7 @@
       <c r="A226">
         <v>225</v>
       </c>
-      <c r="B226" s="16"/>
+      <c r="B226" s="15"/>
       <c r="C226" s="5" t="s">
         <v>50</v>
       </c>
@@ -10057,7 +10172,7 @@
       <c r="A227">
         <v>226</v>
       </c>
-      <c r="B227" s="16"/>
+      <c r="B227" s="15"/>
       <c r="C227" s="5" t="s">
         <v>51</v>
       </c>
@@ -10081,7 +10196,7 @@
       <c r="A228">
         <v>227</v>
       </c>
-      <c r="B228" s="16"/>
+      <c r="B228" s="15"/>
       <c r="C228" s="5" t="s">
         <v>52</v>
       </c>
@@ -10102,209 +10217,930 @@
       </c>
     </row>
     <row r="229" spans="1:8">
-      <c r="A229">
+      <c r="A229" s="17">
         <v>228</v>
       </c>
-      <c r="B229" s="18">
+      <c r="B229" s="19">
         <v>20</v>
       </c>
-      <c r="C229" s="19" t="s">
+      <c r="C229" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D229" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E229" s="17">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="F229" s="17">
+        <v>0.52</v>
+      </c>
+      <c r="G229" s="17">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="H229" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="17">
+        <v>229</v>
+      </c>
+      <c r="B230" s="21"/>
+      <c r="C230" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D230" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E230" s="17">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="F230" s="17">
+        <v>0.52</v>
+      </c>
+      <c r="G230" s="17">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="H230" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" s="17">
+        <v>230</v>
+      </c>
+      <c r="B231" s="21"/>
+      <c r="C231" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D231" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E231" s="17">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="F231" s="17">
+        <v>0.53</v>
+      </c>
+      <c r="G231" s="17">
+        <v>9.44</v>
+      </c>
+      <c r="H231" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" s="17">
+        <v>231</v>
+      </c>
+      <c r="B232" s="21"/>
+      <c r="C232" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D232" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E232" s="17">
+        <v>0.63300000000000001</v>
+      </c>
+      <c r="F232" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G232" s="17">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="H232" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" s="17">
+        <v>232</v>
+      </c>
+      <c r="B233" s="21"/>
+      <c r="C233" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D233" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E233" s="17">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="F233" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G233" s="17">
+        <v>9.57</v>
+      </c>
+      <c r="H233" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="17">
+        <v>233</v>
+      </c>
+      <c r="B234" s="21"/>
+      <c r="C234" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D234" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E234" s="17">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="F234" s="17">
+        <v>0.61</v>
+      </c>
+      <c r="G234" s="17">
+        <v>9.4</v>
+      </c>
+      <c r="H234" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="17">
+        <v>234</v>
+      </c>
+      <c r="B235" s="21"/>
+      <c r="C235" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D235" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E235" s="17">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="F235" s="17">
+        <v>0.51</v>
+      </c>
+      <c r="G235" s="17">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H235" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="17">
+        <v>235</v>
+      </c>
+      <c r="B236" s="21"/>
+      <c r="C236" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D236" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E236" s="17">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="F236" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G236" s="17">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H236" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="17">
+        <v>236</v>
+      </c>
+      <c r="B237" s="21"/>
+      <c r="C237" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D237" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E237" s="17">
+        <v>0.64</v>
+      </c>
+      <c r="F237" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G237" s="17">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="H237" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="17">
+        <v>237</v>
+      </c>
+      <c r="B238" s="21"/>
+      <c r="C238" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D238" s="18">
+        <v>46311</v>
+      </c>
+      <c r="E238" s="17">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="F238" s="17">
+        <v>0.51</v>
+      </c>
+      <c r="G238" s="17">
+        <v>9.18</v>
+      </c>
+      <c r="H238" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="17">
+        <v>238</v>
+      </c>
+      <c r="B239" s="21"/>
+      <c r="C239" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D229" s="17">
+      <c r="D239" s="18">
         <v>46312</v>
       </c>
-      <c r="E229" s="19">
+      <c r="E239" s="17">
         <v>0.63200000000000001</v>
       </c>
-      <c r="F229" s="19">
+      <c r="F239" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="G229" s="19">
+      <c r="G239" s="17">
         <v>8.07</v>
       </c>
-      <c r="H229" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8">
-      <c r="A230">
-        <v>229</v>
-      </c>
-      <c r="B230" s="18"/>
-      <c r="C230" s="19" t="s">
+      <c r="H239" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="17">
+        <v>239</v>
+      </c>
+      <c r="B240" s="21"/>
+      <c r="C240" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D230" s="17">
+      <c r="D240" s="18">
         <v>46312</v>
       </c>
-      <c r="E230" s="19">
+      <c r="E240" s="17">
         <v>0.68600000000000005</v>
       </c>
-      <c r="F230" s="19">
+      <c r="F240" s="17">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G230" s="19">
+      <c r="G240" s="17">
         <v>8.31</v>
       </c>
-      <c r="H230" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8">
-      <c r="A231">
-        <v>230</v>
-      </c>
-      <c r="B231" s="18"/>
-      <c r="C231" s="19" t="s">
+      <c r="H240" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="17">
+        <v>240</v>
+      </c>
+      <c r="B241" s="21"/>
+      <c r="C241" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D231" s="17">
+      <c r="D241" s="18">
         <v>46312</v>
       </c>
-      <c r="E231" s="19">
+      <c r="E241" s="17">
         <v>0.69</v>
       </c>
-      <c r="F231" s="19">
+      <c r="F241" s="17">
         <v>0.52</v>
       </c>
-      <c r="G231" s="19">
+      <c r="G241" s="17">
         <v>8.7899999999999991</v>
       </c>
-      <c r="H231" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8">
-      <c r="A232">
-        <v>231</v>
-      </c>
-      <c r="B232" s="18"/>
-      <c r="C232" s="19" t="s">
+      <c r="H241" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="17">
+        <v>241</v>
+      </c>
+      <c r="B242" s="21"/>
+      <c r="C242" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D232" s="17">
+      <c r="D242" s="18">
         <v>46312</v>
       </c>
-      <c r="E232" s="19">
+      <c r="E242" s="17">
         <v>0.75900000000000001</v>
       </c>
-      <c r="F232" s="19">
+      <c r="F242" s="17">
         <v>0.53</v>
       </c>
-      <c r="G232" s="19">
+      <c r="G242" s="17">
         <v>8.43</v>
       </c>
-      <c r="H232" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8">
-      <c r="A233">
-        <v>232</v>
-      </c>
-      <c r="B233" s="18"/>
-      <c r="C233" s="19" t="s">
+      <c r="H242" s="22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="17">
+        <v>242</v>
+      </c>
+      <c r="B243" s="21"/>
+      <c r="C243" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D233" s="17">
+      <c r="D243" s="18">
         <v>46312</v>
       </c>
-      <c r="E233" s="19">
+      <c r="E243" s="17">
         <v>0.746</v>
       </c>
-      <c r="F233" s="19">
+      <c r="F243" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G233" s="19">
+      <c r="G243" s="17">
         <v>8.5500000000000007</v>
       </c>
-      <c r="H233" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8">
-      <c r="A234">
-        <v>233</v>
-      </c>
-      <c r="B234" s="18"/>
-      <c r="C234" s="19" t="s">
+      <c r="H243" s="22"/>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="17">
+        <v>243</v>
+      </c>
+      <c r="B244" s="21"/>
+      <c r="C244" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D234" s="17">
+      <c r="D244" s="18">
         <v>46312</v>
       </c>
-      <c r="E234" s="19">
+      <c r="E244" s="17">
         <v>0.73299999999999998</v>
       </c>
-      <c r="F234" s="19">
+      <c r="F244" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G234" s="19">
+      <c r="G244" s="17">
         <v>8.49</v>
       </c>
-      <c r="H234" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8">
-      <c r="A235">
-        <v>234</v>
-      </c>
-      <c r="B235" s="18"/>
-      <c r="C235" s="19" t="s">
+      <c r="H244" s="22"/>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="17">
+        <v>244</v>
+      </c>
+      <c r="B245" s="21"/>
+      <c r="C245" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D235" s="17">
+      <c r="D245" s="18">
         <v>46312</v>
       </c>
-      <c r="E235" s="19">
+      <c r="E245" s="17">
         <v>0.72499999999999998</v>
       </c>
-      <c r="F235" s="19">
+      <c r="F245" s="17">
         <v>0.53</v>
       </c>
-      <c r="G235" s="19">
+      <c r="G245" s="17">
         <v>8.14</v>
       </c>
-      <c r="H235" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8">
-      <c r="A236">
-        <v>235</v>
-      </c>
-      <c r="B236" s="18"/>
-      <c r="C236" s="19" t="s">
+      <c r="H245" s="22"/>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="17">
+        <v>245</v>
+      </c>
+      <c r="B246" s="23"/>
+      <c r="C246" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D236" s="17">
+      <c r="D246" s="18">
         <v>46312</v>
       </c>
-      <c r="E236" s="19">
+      <c r="E246" s="17">
         <v>0.73</v>
       </c>
-      <c r="F236" s="19">
+      <c r="F246" s="17">
         <v>0.57999999999999996</v>
       </c>
-      <c r="G236" s="19">
+      <c r="G246" s="17">
         <v>8.57</v>
       </c>
-      <c r="H236" s="20" t="s">
-        <v>29</v>
-      </c>
+      <c r="H246" s="22"/>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" s="24">
+        <v>246</v>
+      </c>
+      <c r="B247" s="25">
+        <v>21</v>
+      </c>
+      <c r="C247" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D247" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E247" s="24">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="F247" s="24">
+        <v>0.61</v>
+      </c>
+      <c r="G247" s="24">
+        <v>10.76</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" s="24">
+        <v>247</v>
+      </c>
+      <c r="B248" s="25"/>
+      <c r="C248" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D248" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E248" s="24">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="F248" s="24">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G248" s="24">
+        <v>11.27</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" s="24">
+        <v>248</v>
+      </c>
+      <c r="B249" s="25"/>
+      <c r="C249" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D249" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E249" s="24">
+        <v>0.45</v>
+      </c>
+      <c r="F249" s="24">
+        <v>0.59</v>
+      </c>
+      <c r="G249" s="24">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" s="24">
+        <v>249</v>
+      </c>
+      <c r="B250" s="25"/>
+      <c r="C250" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D250" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E250" s="24">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="F250" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G250" s="24">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" s="24">
+        <v>250</v>
+      </c>
+      <c r="B251" s="25"/>
+      <c r="C251" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D251" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E251" s="24">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F251" s="24">
+        <v>0.53</v>
+      </c>
+      <c r="G251" s="24">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="24">
+        <v>251</v>
+      </c>
+      <c r="B252" s="25"/>
+      <c r="C252" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D252" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E252" s="24">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="F252" s="24">
+        <v>0.47</v>
+      </c>
+      <c r="G252" s="24">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="24">
+        <v>252</v>
+      </c>
+      <c r="B253" s="25"/>
+      <c r="C253" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D253" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E253" s="24">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="F253" s="24">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="G253" s="24">
+        <v>8.0760000000000005</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="24">
+        <v>253</v>
+      </c>
+      <c r="B254" s="25"/>
+      <c r="C254" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D254" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E254" s="24">
+        <v>0.317</v>
+      </c>
+      <c r="F254" s="24">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="G254" s="24">
+        <v>8.1120000000000001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="24">
+        <v>254</v>
+      </c>
+      <c r="B255" s="25"/>
+      <c r="C255" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D255" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E255" s="24">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="F255" s="24">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="G255" s="24">
+        <v>8.5830000000000002</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="24">
+        <v>255</v>
+      </c>
+      <c r="B256" s="25"/>
+      <c r="C256" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D256" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E256" s="24">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="F256" s="24">
+        <v>0.17</v>
+      </c>
+      <c r="G256" s="24">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257" s="24">
+        <v>256</v>
+      </c>
+      <c r="B257" s="25"/>
+      <c r="C257" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D257" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E257" s="24">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="F257" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="G257" s="24">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258" s="24">
+        <v>257</v>
+      </c>
+      <c r="B258" s="25"/>
+      <c r="C258" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D258" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E258" s="24">
+        <v>0.379</v>
+      </c>
+      <c r="F258" s="24">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G258" s="24">
+        <v>9.859</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259" s="24">
+        <v>258</v>
+      </c>
+      <c r="B259" s="25"/>
+      <c r="C259" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D259" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E259" s="24">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="F259" s="24">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="G259" s="24">
+        <v>10.090999999999999</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260" s="24">
+        <v>259</v>
+      </c>
+      <c r="B260" s="25"/>
+      <c r="C260" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D260" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E260" s="24">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="F260" s="24">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="G260" s="24">
+        <v>9.9169999999999998</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261" s="24">
+        <v>260</v>
+      </c>
+      <c r="B261" s="25"/>
+      <c r="C261" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D261" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E261" s="24">
+        <v>0.435</v>
+      </c>
+      <c r="F261" s="24">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="G261" s="24">
+        <v>9.5419999999999998</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262" s="24">
+        <v>261</v>
+      </c>
+      <c r="B262" s="25"/>
+      <c r="C262" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D262" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E262" s="24">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="F262" s="24">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="G262" s="24">
+        <v>9.6780000000000008</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263" s="24">
+        <v>262</v>
+      </c>
+      <c r="B263" s="25"/>
+      <c r="C263" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D263" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E263" s="24">
+        <v>0.33</v>
+      </c>
+      <c r="F263" s="24">
+        <v>0.15</v>
+      </c>
+      <c r="G263" s="24">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264" s="24">
+        <v>263</v>
+      </c>
+      <c r="B264" s="25"/>
+      <c r="C264" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D264" s="26">
+        <v>46313</v>
+      </c>
+      <c r="E264" s="24">
+        <v>0.311</v>
+      </c>
+      <c r="F264" s="24">
+        <v>0.36</v>
+      </c>
+      <c r="G264" s="24">
+        <v>9.0399999999999991</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265" s="24">
+        <v>264</v>
+      </c>
+      <c r="B265" s="25"/>
+      <c r="C265" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D265" s="26">
+        <v>46314</v>
+      </c>
+      <c r="E265" s="24">
+        <v>0.443</v>
+      </c>
+      <c r="F265" s="24">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G265" s="24">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266" s="24">
+        <v>265</v>
+      </c>
+      <c r="B266" s="25"/>
+      <c r="C266" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D266" s="26">
+        <v>46314</v>
+      </c>
+      <c r="E266" s="24">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="F266" s="24">
+        <v>0.68</v>
+      </c>
+      <c r="G266" s="24">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267" s="24">
+        <v>266</v>
+      </c>
+      <c r="B267" s="25"/>
+      <c r="C267" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D267" s="26">
+        <v>46314</v>
+      </c>
+      <c r="E267" s="24">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="F267" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="G267" s="24">
+        <v>13.18</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268" s="24">
+        <v>267</v>
+      </c>
+      <c r="B268" s="25"/>
+      <c r="C268" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D268" s="26">
+        <v>46314</v>
+      </c>
+      <c r="E268" s="24">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="F268" s="24">
+        <v>0.17</v>
+      </c>
+      <c r="G268" s="24">
+        <v>10.220000000000001</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" s="24">
+        <v>268</v>
+      </c>
+      <c r="B269" s="25"/>
+      <c r="C269" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D269" s="26">
+        <v>46314</v>
+      </c>
+      <c r="E269" s="24">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="F269" s="24">
+        <v>0.32</v>
+      </c>
+      <c r="G269" s="24">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" s="24">
+        <v>269</v>
+      </c>
+      <c r="B270" s="25"/>
+      <c r="C270" s="24"/>
+      <c r="D270" s="26"/>
+      <c r="E270" s="24"/>
+      <c r="F270" s="24"/>
+      <c r="G270" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B229:B236"/>
-    <mergeCell ref="B209:B228"/>
-    <mergeCell ref="B146:B160"/>
-    <mergeCell ref="B161:B169"/>
-    <mergeCell ref="B170:B178"/>
-    <mergeCell ref="B179:B190"/>
-    <mergeCell ref="B191:B199"/>
-    <mergeCell ref="B200:B208"/>
+  <mergeCells count="21">
+    <mergeCell ref="B247:B270"/>
     <mergeCell ref="B128:B145"/>
     <mergeCell ref="B2:B13"/>
     <mergeCell ref="B14:B22"/>
@@ -10317,7 +11153,16 @@
     <mergeCell ref="B86:B97"/>
     <mergeCell ref="B98:B118"/>
     <mergeCell ref="B119:B127"/>
+    <mergeCell ref="B209:B228"/>
+    <mergeCell ref="B146:B160"/>
+    <mergeCell ref="B161:B169"/>
+    <mergeCell ref="B170:B178"/>
+    <mergeCell ref="B179:B190"/>
+    <mergeCell ref="B191:B199"/>
+    <mergeCell ref="B200:B208"/>
+    <mergeCell ref="B229:B246"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>